--- a/rpt_template.xlsx
+++ b/rpt_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\ZhuhaiZg\zkc1601\Resource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\ZhuhaiZg\zkc1601\Resource\report_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27B015B-4193-44A9-A3EF-CE558A632FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FEEC3E-7DF2-465E-9559-1D0B1B4BC22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{8C9C76BE-07CF-46C5-B8D9-D7207282EA5E}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="switch_on" sheetId="1" r:id="rId1"/>
     <sheet name="with_auto_test" sheetId="3" r:id="rId2"/>
     <sheet name="lrt_hvt_zkc_at" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="253">
   <si>
     <t>单位名称:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -937,6 +936,21 @@
   </si>
   <si>
     <t>{{wvt_ac}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C相
+评判</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否
+合格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>试验
+类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -944,7 +958,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1003,19 +1017,37 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="16">
@@ -1201,7 +1233,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1298,149 +1330,164 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1772,23 +1819,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="65"/>
+      <c r="B2" s="64"/>
       <c r="C2" s="3" t="s">
         <v>55</v>
       </c>
@@ -1796,17 +1843,17 @@
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="66" t="s">
+      <c r="F2" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="3" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="65"/>
+      <c r="B3" s="64"/>
       <c r="C3" s="3" t="s">
         <v>57</v>
       </c>
@@ -1814,11 +1861,11 @@
       <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="F3" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
     </row>
     <row r="4" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
@@ -1831,15 +1878,15 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="63" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="64"/>
+      <c r="E5" s="53"/>
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
@@ -1849,15 +1896,15 @@
       <c r="H5" s="68"/>
     </row>
     <row r="6" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="43" t="s">
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="E6" s="44"/>
+      <c r="E6" s="50"/>
       <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
@@ -1870,10 +1917,10 @@
       <c r="A7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="50"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="9" t="s">
         <v>34</v>
       </c>
@@ -1883,19 +1930,19 @@
       <c r="F7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="67" t="s">
+      <c r="G7" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="67"/>
+      <c r="H7" s="75"/>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="44"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="6" t="s">
         <v>60</v>
       </c>
@@ -1914,10 +1961,10 @@
       <c r="A9" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="44"/>
+      <c r="C9" s="50"/>
       <c r="D9" s="6" t="s">
         <v>65</v>
       </c>
@@ -1932,10 +1979,10 @@
       <c r="A10" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="44"/>
+      <c r="C10" s="50"/>
       <c r="D10" s="6" t="s">
         <v>68</v>
       </c>
@@ -1948,20 +1995,20 @@
     </row>
     <row r="11" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="22"/>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="48"/>
+      <c r="C11" s="60"/>
       <c r="D11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="67" t="s">
+      <c r="F11" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="67"/>
+      <c r="G11" s="75"/>
       <c r="H11" s="9" t="s">
         <v>36</v>
       </c>
@@ -1987,16 +2034,16 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="394.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="D14" s="1"/>
@@ -2016,23 +2063,23 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="69" t="s">
+      <c r="A17" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55"/>
     </row>
     <row r="18" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="65" t="s">
+      <c r="A18" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="65"/>
+      <c r="B18" s="64"/>
       <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
@@ -2040,17 +2087,17 @@
       <c r="E18" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F18" s="66" t="s">
+      <c r="F18" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
     </row>
     <row r="19" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="65" t="s">
+      <c r="A19" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="65"/>
+      <c r="B19" s="64"/>
       <c r="C19" s="3" t="s">
         <v>57</v>
       </c>
@@ -2058,11 +2105,11 @@
       <c r="E19" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F19" s="62" t="s">
+      <c r="F19" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
     </row>
     <row r="20" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15"/>
@@ -2075,15 +2122,15 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="48" t="s">
+      <c r="A21" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="70" t="s">
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="70"/>
+      <c r="E21" s="76"/>
       <c r="F21" s="5" t="s">
         <v>12</v>
       </c>
@@ -2093,11 +2140,11 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
       <c r="D22" s="68" t="s">
         <v>177</v>
       </c>
@@ -2114,10 +2161,10 @@
       <c r="A23" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="67"/>
+      <c r="C23" s="75"/>
       <c r="D23" s="9" t="s">
         <v>18</v>
       </c>
@@ -2127,10 +2174,10 @@
       <c r="F23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="67" t="s">
+      <c r="G23" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="H23" s="67"/>
+      <c r="H23" s="75"/>
     </row>
     <row r="24" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="21" t="s">
@@ -2239,16 +2286,16 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="397.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="71" t="s">
+      <c r="A29" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="B29" s="71"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="D30" s="1"/>
@@ -2268,23 +2315,23 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="69" t="s">
+      <c r="A33" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="69"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="69"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55"/>
     </row>
     <row r="34" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="65" t="s">
+      <c r="A34" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="65"/>
+      <c r="B34" s="64"/>
       <c r="C34" s="3" t="s">
         <v>55</v>
       </c>
@@ -2292,17 +2339,17 @@
       <c r="E34" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F34" s="66" t="s">
+      <c r="F34" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="G34" s="66"/>
-      <c r="H34" s="66"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
     </row>
     <row r="35" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="65" t="s">
+      <c r="A35" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B35" s="65"/>
+      <c r="B35" s="64"/>
       <c r="C35" s="3" t="s">
         <v>57</v>
       </c>
@@ -2310,11 +2357,11 @@
       <c r="E35" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F35" s="62" t="s">
+      <c r="F35" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
     </row>
     <row r="36" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="15"/>
@@ -2327,15 +2374,15 @@
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="48" t="s">
+      <c r="A37" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="63" t="s">
+      <c r="B37" s="60"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="E37" s="64"/>
+      <c r="E37" s="53"/>
       <c r="F37" s="5" t="s">
         <v>12</v>
       </c>
@@ -2345,15 +2392,15 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="48" t="s">
+      <c r="A38" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="48"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="43" t="s">
+      <c r="B38" s="60"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="48" t="s">
         <v>178</v>
       </c>
-      <c r="E38" s="44"/>
+      <c r="E38" s="50"/>
       <c r="F38" s="5" t="s">
         <v>13</v>
       </c>
@@ -2363,79 +2410,79 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="45" t="s">
+      <c r="A39" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="60"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="49" t="s">
+      <c r="B39" s="62"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="50"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="57"/>
     </row>
     <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="43" t="s">
+      <c r="A40" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="B40" s="47"/>
-      <c r="C40" s="44"/>
-      <c r="D40" s="43" t="s">
+      <c r="B40" s="49"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="44"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="50"/>
     </row>
     <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="43" t="s">
+      <c r="A41" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="B41" s="47"/>
-      <c r="C41" s="44"/>
-      <c r="D41" s="43" t="s">
+      <c r="B41" s="49"/>
+      <c r="C41" s="50"/>
+      <c r="D41" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="44"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="50"/>
     </row>
     <row r="42" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="43" t="s">
+      <c r="A42" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="B42" s="47"/>
-      <c r="C42" s="44"/>
-      <c r="D42" s="43" t="s">
+      <c r="B42" s="49"/>
+      <c r="C42" s="50"/>
+      <c r="D42" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="44"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="50"/>
     </row>
     <row r="43" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B43" s="49" t="s">
+      <c r="B43" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="50"/>
+      <c r="C43" s="57"/>
       <c r="D43" s="9" t="s">
         <v>34</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F43" s="45" t="s">
+      <c r="F43" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G43" s="46"/>
+      <c r="G43" s="59"/>
       <c r="H43" s="9" t="s">
         <v>19</v>
       </c>
@@ -2444,21 +2491,21 @@
       <c r="A44" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="B44" s="43" t="s">
+      <c r="B44" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="44"/>
+      <c r="C44" s="50"/>
       <c r="D44" s="6" t="s">
         <v>93</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F44" s="54" t="s">
+      <c r="F44" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="G44" s="55"/>
-      <c r="H44" s="51" t="s">
+      <c r="G44" s="70"/>
+      <c r="H44" s="65" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2466,44 +2513,44 @@
       <c r="A45" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="B45" s="43" t="s">
+      <c r="B45" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="44"/>
+      <c r="C45" s="50"/>
       <c r="D45" s="20" t="s">
         <v>98</v>
       </c>
       <c r="E45" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F45" s="56"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="52"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="72"/>
+      <c r="H45" s="66"/>
     </row>
     <row r="46" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="B46" s="43" t="s">
+      <c r="B46" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="44"/>
+      <c r="C46" s="50"/>
       <c r="D46" s="20" t="s">
         <v>101</v>
       </c>
       <c r="E46" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F46" s="58"/>
-      <c r="G46" s="59"/>
-      <c r="H46" s="53"/>
+      <c r="F46" s="73"/>
+      <c r="G46" s="74"/>
+      <c r="H46" s="67"/>
     </row>
     <row r="47" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="48" t="s">
+      <c r="A47" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B47" s="48"/>
-      <c r="C47" s="48"/>
+      <c r="B47" s="60"/>
+      <c r="C47" s="60"/>
       <c r="D47" s="5" t="s">
         <v>10</v>
       </c>
@@ -2521,11 +2568,11 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="43" t="s">
+      <c r="A48" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="B48" s="47"/>
-      <c r="C48" s="44"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="50"/>
       <c r="D48" s="6" t="s">
         <v>103</v>
       </c>
@@ -2546,20 +2593,20 @@
       <c r="A49" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B49" s="49" t="s">
+      <c r="B49" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="C49" s="50"/>
+      <c r="C49" s="57"/>
       <c r="D49" s="9" t="s">
         <v>34</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F49" s="45" t="s">
+      <c r="F49" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="46"/>
+      <c r="G49" s="59"/>
       <c r="H49" s="9" t="s">
         <v>24</v>
       </c>
@@ -2568,21 +2615,21 @@
       <c r="A50" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="B50" s="43" t="s">
+      <c r="B50" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="C50" s="44"/>
+      <c r="C50" s="50"/>
       <c r="D50" s="20" t="s">
         <v>109</v>
       </c>
       <c r="E50" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F50" s="54" t="s">
+      <c r="F50" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="G50" s="55"/>
-      <c r="H50" s="51" t="s">
+      <c r="G50" s="70"/>
+      <c r="H50" s="65" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2590,43 +2637,43 @@
       <c r="A51" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="B51" s="43" t="s">
+      <c r="B51" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="C51" s="44"/>
+      <c r="C51" s="50"/>
       <c r="D51" s="20" t="s">
         <v>114</v>
       </c>
       <c r="E51" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="F51" s="56"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="52"/>
+      <c r="F51" s="71"/>
+      <c r="G51" s="72"/>
+      <c r="H51" s="66"/>
     </row>
     <row r="52" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="B52" s="43" t="s">
+      <c r="B52" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="C52" s="44"/>
+      <c r="C52" s="50"/>
       <c r="D52" s="20" t="s">
         <v>117</v>
       </c>
       <c r="E52" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="F52" s="58"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="53"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="74"/>
+      <c r="H52" s="67"/>
     </row>
     <row r="53" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="45" t="s">
+      <c r="A53" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="B53" s="46"/>
+      <c r="B53" s="59"/>
       <c r="C53" s="9" t="s">
         <v>26</v>
       </c>
@@ -2647,10 +2694,10 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="43" t="s">
+      <c r="A54" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="B54" s="47"/>
+      <c r="B54" s="49"/>
       <c r="C54" s="6" t="s">
         <v>39</v>
       </c>
@@ -2688,45 +2735,45 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="42" t="s">
+      <c r="A58" s="77" t="s">
         <v>203</v>
       </c>
-      <c r="B58" s="42"/>
-      <c r="C58" s="42"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="42"/>
-      <c r="H58" s="42"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="77"/>
+      <c r="E58" s="77"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="77"/>
+      <c r="H58" s="77"/>
     </row>
     <row r="59" spans="1:9" ht="386.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="42"/>
-      <c r="B59" s="42"/>
-      <c r="C59" s="42"/>
-      <c r="D59" s="42"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="42"/>
-      <c r="H59" s="42"/>
+      <c r="A59" s="77"/>
+      <c r="B59" s="77"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="77"/>
+      <c r="E59" s="77"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="77"/>
     </row>
     <row r="62" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="69" t="s">
+      <c r="A62" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B62" s="69"/>
-      <c r="C62" s="69"/>
-      <c r="D62" s="69"/>
-      <c r="E62" s="69"/>
-      <c r="F62" s="69"/>
-      <c r="G62" s="69"/>
-      <c r="H62" s="69"/>
-      <c r="I62" s="69"/>
+      <c r="B62" s="55"/>
+      <c r="C62" s="55"/>
+      <c r="D62" s="55"/>
+      <c r="E62" s="55"/>
+      <c r="F62" s="55"/>
+      <c r="G62" s="55"/>
+      <c r="H62" s="55"/>
+      <c r="I62" s="55"/>
     </row>
     <row r="63" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="65" t="s">
+      <c r="A63" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B63" s="65"/>
+      <c r="B63" s="64"/>
       <c r="C63" s="3" t="s">
         <v>55</v>
       </c>
@@ -2734,17 +2781,17 @@
       <c r="E63" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F63" s="66" t="s">
+      <c r="F63" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="G63" s="66"/>
-      <c r="H63" s="66"/>
+      <c r="G63" s="61"/>
+      <c r="H63" s="61"/>
     </row>
     <row r="64" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="65" t="s">
+      <c r="A64" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B64" s="65"/>
+      <c r="B64" s="64"/>
       <c r="C64" s="3" t="s">
         <v>57</v>
       </c>
@@ -2752,11 +2799,11 @@
       <c r="E64" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F64" s="62" t="s">
+      <c r="F64" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="G64" s="62"/>
-      <c r="H64" s="62"/>
+      <c r="G64" s="51"/>
+      <c r="H64" s="51"/>
     </row>
     <row r="65" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="15"/>
@@ -2769,15 +2816,15 @@
       <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="48" t="s">
+      <c r="A66" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B66" s="48"/>
-      <c r="C66" s="48"/>
-      <c r="D66" s="63" t="s">
+      <c r="B66" s="60"/>
+      <c r="C66" s="60"/>
+      <c r="D66" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="E66" s="64"/>
+      <c r="E66" s="53"/>
       <c r="F66" s="5" t="s">
         <v>12</v>
       </c>
@@ -2787,15 +2834,15 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="48" t="s">
+      <c r="A67" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B67" s="48"/>
-      <c r="C67" s="48"/>
-      <c r="D67" s="43" t="s">
+      <c r="B67" s="60"/>
+      <c r="C67" s="60"/>
+      <c r="D67" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="E67" s="44"/>
+      <c r="E67" s="50"/>
       <c r="F67" s="5" t="s">
         <v>13</v>
       </c>
@@ -2805,87 +2852,87 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="18" x14ac:dyDescent="0.2">
-      <c r="A68" s="45" t="s">
+      <c r="A68" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B68" s="60"/>
-      <c r="C68" s="46"/>
-      <c r="D68" s="49" t="s">
+      <c r="B68" s="62"/>
+      <c r="C68" s="59"/>
+      <c r="D68" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="E68" s="61"/>
-      <c r="F68" s="61"/>
-      <c r="G68" s="61" t="s">
+      <c r="E68" s="63"/>
+      <c r="F68" s="63"/>
+      <c r="G68" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="H68" s="50"/>
+      <c r="H68" s="57"/>
     </row>
     <row r="69" spans="1:8" ht="18" x14ac:dyDescent="0.2">
-      <c r="A69" s="43" t="s">
+      <c r="A69" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B69" s="47"/>
-      <c r="C69" s="44"/>
-      <c r="D69" s="43" t="s">
+      <c r="B69" s="49"/>
+      <c r="C69" s="50"/>
+      <c r="D69" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
-      <c r="G69" s="47" t="s">
+      <c r="E69" s="49"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="H69" s="44"/>
+      <c r="H69" s="50"/>
     </row>
     <row r="70" spans="1:8" ht="18" x14ac:dyDescent="0.2">
-      <c r="A70" s="43" t="s">
+      <c r="A70" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="B70" s="47"/>
-      <c r="C70" s="44"/>
-      <c r="D70" s="43" t="s">
+      <c r="B70" s="49"/>
+      <c r="C70" s="50"/>
+      <c r="D70" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="E70" s="47"/>
-      <c r="F70" s="47"/>
-      <c r="G70" s="47" t="s">
+      <c r="E70" s="49"/>
+      <c r="F70" s="49"/>
+      <c r="G70" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="H70" s="44"/>
+      <c r="H70" s="50"/>
     </row>
     <row r="71" spans="1:8" ht="18" x14ac:dyDescent="0.2">
-      <c r="A71" s="43" t="s">
+      <c r="A71" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="B71" s="47"/>
-      <c r="C71" s="44"/>
-      <c r="D71" s="43" t="s">
+      <c r="B71" s="49"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47" t="s">
+      <c r="E71" s="49"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="H71" s="44"/>
+      <c r="H71" s="50"/>
     </row>
     <row r="72" spans="1:8" ht="36" x14ac:dyDescent="0.2">
       <c r="A72" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B72" s="49" t="s">
+      <c r="B72" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="C72" s="50"/>
+      <c r="C72" s="57"/>
       <c r="D72" s="14" t="s">
         <v>34</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F72" s="45" t="s">
+      <c r="F72" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="46"/>
+      <c r="G72" s="59"/>
       <c r="H72" s="14" t="s">
         <v>46</v>
       </c>
@@ -2894,21 +2941,21 @@
       <c r="A73" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B73" s="43" t="s">
+      <c r="B73" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="C73" s="44"/>
+      <c r="C73" s="50"/>
       <c r="D73" s="13" t="s">
         <v>131</v>
       </c>
       <c r="E73" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F73" s="54" t="s">
+      <c r="F73" s="69" t="s">
         <v>133</v>
       </c>
-      <c r="G73" s="55"/>
-      <c r="H73" s="51" t="s">
+      <c r="G73" s="70"/>
+      <c r="H73" s="65" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2916,43 +2963,43 @@
       <c r="A74" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="B74" s="43" t="s">
+      <c r="B74" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="C74" s="44"/>
+      <c r="C74" s="50"/>
       <c r="D74" s="20" t="s">
         <v>136</v>
       </c>
       <c r="E74" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="F74" s="56"/>
-      <c r="G74" s="57"/>
-      <c r="H74" s="52"/>
+      <c r="F74" s="71"/>
+      <c r="G74" s="72"/>
+      <c r="H74" s="66"/>
     </row>
     <row r="75" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B75" s="43" t="s">
+      <c r="B75" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="C75" s="44"/>
+      <c r="C75" s="50"/>
       <c r="D75" s="20" t="s">
         <v>139</v>
       </c>
       <c r="E75" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="F75" s="58"/>
-      <c r="G75" s="59"/>
-      <c r="H75" s="53"/>
+      <c r="F75" s="73"/>
+      <c r="G75" s="74"/>
+      <c r="H75" s="67"/>
     </row>
     <row r="76" spans="1:8" ht="36" x14ac:dyDescent="0.2">
-      <c r="A76" s="45" t="s">
+      <c r="A76" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="B76" s="46"/>
+      <c r="B76" s="59"/>
       <c r="C76" s="14" t="s">
         <v>26</v>
       </c>
@@ -2973,10 +3020,10 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="43" t="s">
+      <c r="A77" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="B77" s="47"/>
+      <c r="B77" s="49"/>
       <c r="C77" s="13" t="s">
         <v>39</v>
       </c>
@@ -3000,20 +3047,20 @@
       <c r="A78" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B78" s="49" t="s">
+      <c r="B78" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="50"/>
+      <c r="C78" s="57"/>
       <c r="D78" s="14" t="s">
         <v>34</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F78" s="45" t="s">
+      <c r="F78" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G78" s="46"/>
+      <c r="G78" s="59"/>
       <c r="H78" s="14" t="s">
         <v>19</v>
       </c>
@@ -3022,21 +3069,21 @@
       <c r="A79" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B79" s="43" t="s">
+      <c r="B79" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="C79" s="44"/>
+      <c r="C79" s="50"/>
       <c r="D79" s="20" t="s">
         <v>147</v>
       </c>
       <c r="E79" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F79" s="54" t="s">
+      <c r="F79" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="G79" s="55"/>
-      <c r="H79" s="51" t="s">
+      <c r="G79" s="70"/>
+      <c r="H79" s="65" t="s">
         <v>150</v>
       </c>
     </row>
@@ -3044,44 +3091,44 @@
       <c r="A80" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="B80" s="43" t="s">
+      <c r="B80" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="C80" s="44"/>
+      <c r="C80" s="50"/>
       <c r="D80" s="20" t="s">
         <v>152</v>
       </c>
       <c r="E80" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="F80" s="56"/>
-      <c r="G80" s="57"/>
-      <c r="H80" s="52"/>
+      <c r="F80" s="71"/>
+      <c r="G80" s="72"/>
+      <c r="H80" s="66"/>
     </row>
     <row r="81" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B81" s="43" t="s">
+      <c r="B81" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="C81" s="44"/>
+      <c r="C81" s="50"/>
       <c r="D81" s="20" t="s">
         <v>155</v>
       </c>
       <c r="E81" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="F81" s="58"/>
-      <c r="G81" s="59"/>
-      <c r="H81" s="53"/>
+      <c r="F81" s="73"/>
+      <c r="G81" s="74"/>
+      <c r="H81" s="67"/>
     </row>
     <row r="82" spans="1:9" ht="36" x14ac:dyDescent="0.2">
-      <c r="A82" s="48" t="s">
+      <c r="A82" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B82" s="48"/>
-      <c r="C82" s="48"/>
+      <c r="B82" s="60"/>
+      <c r="C82" s="60"/>
       <c r="D82" s="5" t="s">
         <v>10</v>
       </c>
@@ -3099,11 +3146,11 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="43" t="s">
+      <c r="A83" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="B83" s="47"/>
-      <c r="C83" s="44"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="50"/>
       <c r="D83" s="6" t="s">
         <v>157</v>
       </c>
@@ -3124,20 +3171,20 @@
       <c r="A84" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B84" s="49" t="s">
+      <c r="B84" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="C84" s="50"/>
+      <c r="C84" s="57"/>
       <c r="D84" s="9" t="s">
         <v>34</v>
       </c>
       <c r="E84" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F84" s="45" t="s">
+      <c r="F84" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G84" s="46"/>
+      <c r="G84" s="59"/>
       <c r="H84" s="9" t="s">
         <v>24</v>
       </c>
@@ -3146,21 +3193,21 @@
       <c r="A85" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B85" s="43" t="s">
+      <c r="B85" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="C85" s="44"/>
+      <c r="C85" s="50"/>
       <c r="D85" s="20" t="s">
         <v>163</v>
       </c>
       <c r="E85" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="F85" s="54" t="s">
+      <c r="F85" s="69" t="s">
         <v>165</v>
       </c>
-      <c r="G85" s="55"/>
-      <c r="H85" s="51" t="s">
+      <c r="G85" s="70"/>
+      <c r="H85" s="65" t="s">
         <v>166</v>
       </c>
     </row>
@@ -3168,43 +3215,43 @@
       <c r="A86" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="B86" s="43" t="s">
+      <c r="B86" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="C86" s="44"/>
+      <c r="C86" s="50"/>
       <c r="D86" s="20" t="s">
         <v>168</v>
       </c>
       <c r="E86" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F86" s="56"/>
-      <c r="G86" s="57"/>
-      <c r="H86" s="52"/>
+      <c r="F86" s="71"/>
+      <c r="G86" s="72"/>
+      <c r="H86" s="66"/>
     </row>
     <row r="87" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B87" s="43" t="s">
+      <c r="B87" s="48" t="s">
         <v>170</v>
       </c>
-      <c r="C87" s="44"/>
+      <c r="C87" s="50"/>
       <c r="D87" s="20" t="s">
         <v>171</v>
       </c>
       <c r="E87" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="F87" s="58"/>
-      <c r="G87" s="59"/>
-      <c r="H87" s="53"/>
+      <c r="F87" s="73"/>
+      <c r="G87" s="74"/>
+      <c r="H87" s="67"/>
     </row>
     <row r="88" spans="1:9" ht="36" x14ac:dyDescent="0.2">
-      <c r="A88" s="45" t="s">
+      <c r="A88" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="B88" s="46"/>
+      <c r="B88" s="59"/>
       <c r="C88" s="9" t="s">
         <v>26</v>
       </c>
@@ -3225,10 +3272,10 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="43" t="s">
+      <c r="A89" s="48" t="s">
         <v>199</v>
       </c>
-      <c r="B89" s="47"/>
+      <c r="B89" s="49"/>
       <c r="C89" s="6" t="s">
         <v>39</v>
       </c>
@@ -3268,29 +3315,130 @@
     </row>
     <row r="93" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="94" spans="1:9" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="42" t="s">
+      <c r="A94" s="77" t="s">
         <v>202</v>
       </c>
-      <c r="B94" s="42"/>
-      <c r="C94" s="42"/>
-      <c r="D94" s="42"/>
-      <c r="E94" s="42"/>
-      <c r="F94" s="42"/>
-      <c r="G94" s="42"/>
-      <c r="H94" s="42"/>
+      <c r="B94" s="77"/>
+      <c r="C94" s="77"/>
+      <c r="D94" s="77"/>
+      <c r="E94" s="77"/>
+      <c r="F94" s="77"/>
+      <c r="G94" s="77"/>
+      <c r="H94" s="77"/>
     </row>
     <row r="95" spans="1:9" ht="378" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="42"/>
-      <c r="B95" s="42"/>
-      <c r="C95" s="42"/>
-      <c r="D95" s="42"/>
-      <c r="E95" s="42"/>
-      <c r="F95" s="42"/>
-      <c r="G95" s="42"/>
-      <c r="H95" s="42"/>
+      <c r="A95" s="77"/>
+      <c r="B95" s="77"/>
+      <c r="C95" s="77"/>
+      <c r="D95" s="77"/>
+      <c r="E95" s="77"/>
+      <c r="F95" s="77"/>
+      <c r="G95" s="77"/>
+      <c r="H95" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="125">
+    <mergeCell ref="A94:H95"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="H85:H87"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G87"/>
+    <mergeCell ref="H79:H81"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="F73:G75"/>
+    <mergeCell ref="H73:H75"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="F79:G81"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A58:H59"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="F50:G52"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="G8:H10"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="H44:H46"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G46"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H26"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="D5:E5"/>
@@ -3315,107 +3463,6 @@
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="B45:C45"/>
-    <mergeCell ref="H44:H46"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G46"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H26"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="G8:H10"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A58:H59"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="F50:G52"/>
-    <mergeCell ref="H50:H52"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="H79:H81"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="F73:G75"/>
-    <mergeCell ref="H73:H75"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="F79:G81"/>
-    <mergeCell ref="A94:H95"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="H85:H87"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3450,68 +3497,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
     </row>
     <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="66" t="s">
+      <c r="B2" s="64"/>
+      <c r="C2" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
       <c r="G2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="2"/>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
     </row>
     <row r="3" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="66" t="s">
+      <c r="B3" s="64"/>
+      <c r="C3" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
       <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="2"/>
-      <c r="I3" s="62" t="s">
+      <c r="I3" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
     </row>
     <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
@@ -3529,22 +3576,22 @@
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="63" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="45" t="s">
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="46"/>
+      <c r="J5" s="59"/>
       <c r="K5" s="68" t="s">
         <v>54</v>
       </c>
@@ -3552,22 +3599,22 @@
       <c r="M5" s="68"/>
     </row>
     <row r="6" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="43" t="s">
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="45" t="s">
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="46"/>
+      <c r="J6" s="59"/>
       <c r="K6" s="68">
         <v>1</v>
       </c>
@@ -3578,50 +3625,50 @@
       <c r="A7" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="50"/>
-      <c r="D7" s="49" t="s">
+      <c r="C7" s="57"/>
+      <c r="D7" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="61"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="45" t="s">
+      <c r="E7" s="63"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="46"/>
-      <c r="I7" s="45" t="s">
+      <c r="H7" s="59"/>
+      <c r="I7" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="46"/>
-      <c r="K7" s="67" t="s">
+      <c r="J7" s="59"/>
+      <c r="K7" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="67"/>
-      <c r="M7" s="67"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
     </row>
     <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="43" t="s">
+      <c r="C8" s="50"/>
+      <c r="D8" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="34" t="s">
+      <c r="E8" s="49"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="54" t="s">
+      <c r="H8" s="33"/>
+      <c r="I8" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="55"/>
+      <c r="J8" s="70"/>
       <c r="K8" s="68" t="s">
         <v>63</v>
       </c>
@@ -3632,21 +3679,21 @@
       <c r="A9" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="43" t="s">
+      <c r="C9" s="50"/>
+      <c r="D9" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="47"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="34" t="s">
+      <c r="E9" s="49"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="35"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="57"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
       <c r="K9" s="68"/>
       <c r="L9" s="68"/>
       <c r="M9" s="68"/>
@@ -3655,49 +3702,49 @@
       <c r="A10" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="43" t="s">
+      <c r="C10" s="50"/>
+      <c r="D10" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="47"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="34" t="s">
+      <c r="E10" s="49"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="35"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="59"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="74"/>
       <c r="K10" s="68"/>
       <c r="L10" s="68"/>
       <c r="M10" s="68"/>
     </row>
     <row r="11" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="22"/>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="45" t="s">
+      <c r="C11" s="60"/>
+      <c r="D11" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="60"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="45" t="s">
+      <c r="E11" s="62"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="46"/>
-      <c r="I11" s="49" t="s">
+      <c r="H11" s="59"/>
+      <c r="I11" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="61"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="49" t="s">
+      <c r="J11" s="63"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="M11" s="50"/>
+      <c r="M11" s="57"/>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
@@ -3705,41 +3752,41 @@
         <v>194</v>
       </c>
       <c r="C12" s="68"/>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="47"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="43" t="s">
+      <c r="E12" s="49"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="H12" s="44"/>
-      <c r="I12" s="43" t="s">
+      <c r="H12" s="50"/>
+      <c r="I12" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="J12" s="47"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="43" t="s">
+      <c r="J12" s="49"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="M12" s="44"/>
+      <c r="M12" s="50"/>
     </row>
     <row r="13" spans="1:14" ht="401.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="71"/>
-      <c r="M13" s="71"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="F14" s="1"/>
@@ -3761,68 +3808,68 @@
       <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="69" t="s">
+      <c r="A16" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="69"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="69"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="55"/>
     </row>
     <row r="17" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="66" t="s">
+      <c r="B17" s="64"/>
+      <c r="C17" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
       <c r="G17" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H17" s="2"/>
-      <c r="I17" s="66" t="s">
+      <c r="I17" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="J17" s="66"/>
-      <c r="K17" s="66"/>
-      <c r="L17" s="66"/>
-      <c r="M17" s="66"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="61"/>
     </row>
     <row r="18" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="65" t="s">
+      <c r="A18" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="65"/>
-      <c r="C18" s="66" t="s">
+      <c r="B18" s="64"/>
+      <c r="C18" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
       <c r="G18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="2"/>
-      <c r="I18" s="62" t="s">
+      <c r="I18" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="62"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="51"/>
+      <c r="M18" s="51"/>
     </row>
     <row r="19" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
@@ -3840,77 +3887,77 @@
       <c r="M19" s="4"/>
     </row>
     <row r="20" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="63" t="s">
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="45" t="s">
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="J20" s="46"/>
-      <c r="K20" s="43" t="s">
+      <c r="J20" s="59"/>
+      <c r="K20" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="L20" s="47"/>
-      <c r="M20" s="44"/>
+      <c r="L20" s="49"/>
+      <c r="M20" s="50"/>
     </row>
     <row r="21" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="48" t="s">
+      <c r="A21" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="43" t="s">
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="48" t="s">
         <v>177</v>
       </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="45" t="s">
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="46"/>
-      <c r="K21" s="43">
+      <c r="J21" s="59"/>
+      <c r="K21" s="48">
         <v>1</v>
       </c>
-      <c r="L21" s="47"/>
-      <c r="M21" s="44"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="50"/>
     </row>
     <row r="22" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="67"/>
-      <c r="D22" s="49" t="s">
+      <c r="C22" s="75"/>
+      <c r="D22" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="61"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="49" t="s">
+      <c r="E22" s="63"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="H22" s="50"/>
-      <c r="I22" s="49" t="s">
+      <c r="H22" s="57"/>
+      <c r="I22" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="J22" s="50"/>
-      <c r="K22" s="67" t="s">
+      <c r="J22" s="57"/>
+      <c r="K22" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="L22" s="67"/>
-      <c r="M22" s="67"/>
+      <c r="L22" s="75"/>
+      <c r="M22" s="75"/>
     </row>
     <row r="23" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
@@ -3920,19 +3967,19 @@
         <v>74</v>
       </c>
       <c r="C23" s="68"/>
-      <c r="D23" s="43" t="s">
+      <c r="D23" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="43" t="s">
+      <c r="E23" s="49"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="H23" s="44"/>
-      <c r="I23" s="54" t="s">
+      <c r="H23" s="50"/>
+      <c r="I23" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="J23" s="55"/>
+      <c r="J23" s="70"/>
       <c r="K23" s="68" t="s">
         <v>78</v>
       </c>
@@ -3947,17 +3994,17 @@
         <v>79</v>
       </c>
       <c r="C24" s="68"/>
-      <c r="D24" s="43" t="s">
+      <c r="D24" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="43" t="s">
+      <c r="E24" s="49"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="H24" s="44"/>
-      <c r="I24" s="56"/>
-      <c r="J24" s="57"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
       <c r="K24" s="68"/>
       <c r="L24" s="68"/>
       <c r="M24" s="68"/>
@@ -3970,95 +4017,95 @@
         <v>82</v>
       </c>
       <c r="C25" s="68"/>
-      <c r="D25" s="43" t="s">
+      <c r="D25" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="47"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="43" t="s">
+      <c r="E25" s="49"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="H25" s="44"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="59"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="74"/>
       <c r="K25" s="68"/>
       <c r="L25" s="68"/>
       <c r="M25" s="68"/>
     </row>
     <row r="26" spans="1:14" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="49" t="s">
+      <c r="A26" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="50"/>
-      <c r="C26" s="49" t="s">
+      <c r="B26" s="57"/>
+      <c r="C26" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="50"/>
-      <c r="E26" s="49" t="s">
+      <c r="D26" s="57"/>
+      <c r="E26" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="50"/>
-      <c r="G26" s="49" t="s">
+      <c r="F26" s="57"/>
+      <c r="G26" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="H26" s="50"/>
-      <c r="I26" s="49" t="s">
+      <c r="H26" s="57"/>
+      <c r="I26" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="J26" s="50"/>
+      <c r="J26" s="57"/>
       <c r="K26" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="L26" s="49" t="s">
+      <c r="L26" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="M26" s="50"/>
+      <c r="M26" s="57"/>
     </row>
     <row r="27" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="44"/>
-      <c r="C27" s="43" t="s">
+      <c r="B27" s="50"/>
+      <c r="C27" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="43" t="s">
+      <c r="D27" s="50"/>
+      <c r="E27" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="F27" s="44"/>
-      <c r="G27" s="43" t="s">
+      <c r="F27" s="50"/>
+      <c r="G27" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="H27" s="44"/>
-      <c r="I27" s="43" t="s">
+      <c r="H27" s="50"/>
+      <c r="I27" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="J27" s="44"/>
+      <c r="J27" s="50"/>
       <c r="K27" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="L27" s="74" t="s">
+      <c r="L27" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="M27" s="75"/>
+      <c r="M27" s="79"/>
     </row>
     <row r="28" spans="1:14" ht="397.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="71" t="s">
+      <c r="A28" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="71"/>
-      <c r="L28" s="71"/>
-      <c r="M28" s="71"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="54"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="F29" s="1"/>
@@ -4080,68 +4127,68 @@
       <c r="L30" s="1"/>
     </row>
     <row r="31" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="69" t="s">
+      <c r="A31" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="69"/>
-      <c r="L31" s="69"/>
-      <c r="M31" s="69"/>
-      <c r="N31" s="69"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="55"/>
     </row>
     <row r="32" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="65" t="s">
+      <c r="A32" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="65"/>
-      <c r="C32" s="66" t="s">
+      <c r="B32" s="64"/>
+      <c r="C32" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="66"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
       <c r="G32" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H32" s="2"/>
-      <c r="I32" s="66" t="s">
+      <c r="I32" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="J32" s="66"/>
-      <c r="K32" s="66"/>
-      <c r="L32" s="66"/>
-      <c r="M32" s="66"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="61"/>
     </row>
     <row r="33" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="65" t="s">
+      <c r="A33" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="65"/>
-      <c r="C33" s="66" t="s">
+      <c r="B33" s="64"/>
+      <c r="C33" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="66"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="66"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
       <c r="G33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H33" s="2"/>
-      <c r="I33" s="62" t="s">
+      <c r="I33" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="J33" s="62"/>
-      <c r="K33" s="62"/>
-      <c r="L33" s="62"/>
-      <c r="M33" s="62"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="51"/>
+      <c r="L33" s="51"/>
+      <c r="M33" s="51"/>
     </row>
     <row r="34" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="15"/>
@@ -4159,166 +4206,166 @@
       <c r="M34" s="4"/>
     </row>
     <row r="35" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="48" t="s">
+      <c r="A35" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="63" t="s">
+      <c r="B35" s="60"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="45" t="s">
+      <c r="E35" s="80"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="J35" s="46"/>
-      <c r="K35" s="43" t="s">
+      <c r="J35" s="59"/>
+      <c r="K35" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="L35" s="47"/>
-      <c r="M35" s="44"/>
+      <c r="L35" s="49"/>
+      <c r="M35" s="50"/>
     </row>
     <row r="36" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="43" t="s">
+      <c r="B36" s="60"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="48" t="s">
         <v>178</v>
       </c>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="45" t="s">
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="J36" s="46"/>
-      <c r="K36" s="43">
+      <c r="J36" s="59"/>
+      <c r="K36" s="48">
         <v>1</v>
       </c>
-      <c r="L36" s="47"/>
-      <c r="M36" s="44"/>
+      <c r="L36" s="49"/>
+      <c r="M36" s="50"/>
     </row>
     <row r="37" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="45" t="s">
+      <c r="A37" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="60"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="49" t="s">
+      <c r="B37" s="62"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="61"/>
-      <c r="M37" s="50"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="63"/>
+      <c r="K37" s="63"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="57"/>
     </row>
     <row r="38" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="43" t="s">
+      <c r="A38" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="B38" s="47"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="43" t="s">
+      <c r="B38" s="49"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="47"/>
-      <c r="I38" s="47"/>
-      <c r="J38" s="47"/>
-      <c r="K38" s="47"/>
-      <c r="L38" s="47"/>
-      <c r="M38" s="44"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="49"/>
+      <c r="K38" s="49"/>
+      <c r="L38" s="49"/>
+      <c r="M38" s="50"/>
     </row>
     <row r="39" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="43" t="s">
+      <c r="A39" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="B39" s="47"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="43" t="s">
+      <c r="B39" s="49"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="47"/>
-      <c r="I39" s="47"/>
-      <c r="J39" s="47"/>
-      <c r="K39" s="47"/>
-      <c r="L39" s="47"/>
-      <c r="M39" s="44"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="49"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
+      <c r="J39" s="49"/>
+      <c r="K39" s="49"/>
+      <c r="L39" s="49"/>
+      <c r="M39" s="50"/>
     </row>
     <row r="40" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="43" t="s">
+      <c r="A40" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="B40" s="47"/>
-      <c r="C40" s="44"/>
-      <c r="D40" s="43" t="s">
+      <c r="B40" s="49"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="47"/>
-      <c r="I40" s="47"/>
-      <c r="J40" s="47"/>
-      <c r="K40" s="47"/>
-      <c r="L40" s="47"/>
-      <c r="M40" s="44"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
+      <c r="J40" s="49"/>
+      <c r="K40" s="49"/>
+      <c r="L40" s="49"/>
+      <c r="M40" s="50"/>
     </row>
     <row r="41" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="49" t="s">
+      <c r="B41" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="C41" s="50"/>
-      <c r="D41" s="49" t="s">
+      <c r="C41" s="57"/>
+      <c r="D41" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="E41" s="50"/>
-      <c r="F41" s="45" t="s">
+      <c r="E41" s="57"/>
+      <c r="F41" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="G41" s="60"/>
-      <c r="H41" s="46"/>
-      <c r="I41" s="45" t="s">
+      <c r="G41" s="62"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="60"/>
-      <c r="K41" s="46"/>
-      <c r="L41" s="49" t="s">
+      <c r="J41" s="62"/>
+      <c r="K41" s="59"/>
+      <c r="L41" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="M41" s="50"/>
+      <c r="M41" s="57"/>
     </row>
     <row r="42" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="B42" s="43" t="s">
+      <c r="B42" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="C42" s="44"/>
-      <c r="D42" s="43" t="s">
+      <c r="C42" s="50"/>
+      <c r="D42" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="E42" s="44"/>
+      <c r="E42" s="50"/>
       <c r="F42" s="68" t="s">
         <v>94</v>
       </c>
@@ -4338,14 +4385,14 @@
       <c r="A43" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="B43" s="43" t="s">
+      <c r="B43" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="C43" s="44"/>
-      <c r="D43" s="43" t="s">
+      <c r="C43" s="50"/>
+      <c r="D43" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="E43" s="44"/>
+      <c r="E43" s="50"/>
       <c r="F43" s="68" t="s">
         <v>99</v>
       </c>
@@ -4361,14 +4408,14 @@
       <c r="A44" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="B44" s="43" t="s">
+      <c r="B44" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="C44" s="44"/>
-      <c r="D44" s="43" t="s">
+      <c r="C44" s="50"/>
+      <c r="D44" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="E44" s="44"/>
+      <c r="E44" s="50"/>
       <c r="F44" s="68" t="s">
         <v>102</v>
       </c>
@@ -4381,31 +4428,31 @@
       <c r="M44" s="68"/>
     </row>
     <row r="45" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="48" t="s">
+      <c r="A45" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B45" s="48"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="48" t="s">
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48" t="s">
+      <c r="E45" s="60"/>
+      <c r="F45" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="G45" s="48"/>
-      <c r="H45" s="67" t="s">
+      <c r="G45" s="60"/>
+      <c r="H45" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="I45" s="67"/>
-      <c r="J45" s="67" t="s">
+      <c r="I45" s="75"/>
+      <c r="J45" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K45" s="67"/>
-      <c r="L45" s="67" t="s">
+      <c r="K45" s="75"/>
+      <c r="L45" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="M45" s="67"/>
+      <c r="M45" s="75"/>
     </row>
     <row r="46" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="68" t="s">
@@ -4438,37 +4485,37 @@
       <c r="A47" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B47" s="49" t="s">
+      <c r="B47" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="50"/>
-      <c r="D47" s="49" t="s">
+      <c r="C47" s="57"/>
+      <c r="D47" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="61"/>
-      <c r="F47" s="50"/>
-      <c r="G47" s="45" t="s">
+      <c r="E47" s="63"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="60"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="45" t="s">
+      <c r="H47" s="62"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="46"/>
-      <c r="L47" s="49" t="s">
+      <c r="K47" s="59"/>
+      <c r="L47" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="M47" s="50"/>
+      <c r="M47" s="57"/>
     </row>
     <row r="48" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="B48" s="43" t="s">
+      <c r="B48" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="44"/>
+      <c r="C48" s="50"/>
       <c r="D48" s="68" t="s">
         <v>109</v>
       </c>
@@ -4492,10 +4539,10 @@
       <c r="A49" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="B49" s="43" t="s">
+      <c r="B49" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="C49" s="44"/>
+      <c r="C49" s="50"/>
       <c r="D49" s="68" t="s">
         <v>114</v>
       </c>
@@ -4515,10 +4562,10 @@
       <c r="A50" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="B50" s="43" t="s">
+      <c r="B50" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="C50" s="44"/>
+      <c r="C50" s="50"/>
       <c r="D50" s="68" t="s">
         <v>117</v>
       </c>
@@ -4535,33 +4582,33 @@
       <c r="M50" s="68"/>
     </row>
     <row r="51" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="48" t="s">
+      <c r="A51" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="48"/>
+      <c r="B51" s="60"/>
       <c r="C51" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D51" s="48" t="s">
+      <c r="D51" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="48"/>
-      <c r="F51" s="67" t="s">
+      <c r="E51" s="60"/>
+      <c r="F51" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="G51" s="67"/>
-      <c r="H51" s="67" t="s">
+      <c r="G51" s="75"/>
+      <c r="H51" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="I51" s="67"/>
-      <c r="J51" s="67" t="s">
+      <c r="I51" s="75"/>
+      <c r="J51" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="K51" s="67"/>
-      <c r="L51" s="67" t="s">
+      <c r="K51" s="75"/>
+      <c r="L51" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="M51" s="67"/>
+      <c r="M51" s="75"/>
     </row>
     <row r="52" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="68" t="s">
@@ -4612,118 +4659,118 @@
       <c r="L54" s="1"/>
     </row>
     <row r="56" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="42" t="s">
+      <c r="A56" s="77" t="s">
         <v>203</v>
       </c>
-      <c r="B56" s="42"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="42"/>
-      <c r="E56" s="42"/>
-      <c r="F56" s="42"/>
-      <c r="G56" s="42"/>
-      <c r="H56" s="42"/>
-      <c r="I56" s="42"/>
-      <c r="J56" s="42"/>
-      <c r="K56" s="42"/>
-      <c r="L56" s="42"/>
-      <c r="M56" s="42"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="77"/>
+      <c r="E56" s="77"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="77"/>
+      <c r="I56" s="77"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="77"/>
+      <c r="L56" s="77"/>
+      <c r="M56" s="77"/>
     </row>
     <row r="57" spans="1:14" ht="386.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="42"/>
-      <c r="B57" s="42"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="42"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="42"/>
-      <c r="I57" s="42"/>
-      <c r="J57" s="42"/>
-      <c r="K57" s="42"/>
-      <c r="L57" s="42"/>
-      <c r="M57" s="42"/>
+      <c r="A57" s="77"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="77"/>
+      <c r="E57" s="77"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="77"/>
+      <c r="H57" s="77"/>
+      <c r="I57" s="77"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="77"/>
+      <c r="L57" s="77"/>
+      <c r="M57" s="77"/>
     </row>
     <row r="60" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="69" t="s">
+      <c r="A60" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B60" s="69"/>
-      <c r="C60" s="69"/>
-      <c r="D60" s="69"/>
-      <c r="E60" s="69"/>
-      <c r="F60" s="69"/>
-      <c r="G60" s="69"/>
-      <c r="H60" s="69"/>
-      <c r="I60" s="69"/>
-      <c r="J60" s="69"/>
-      <c r="K60" s="69"/>
-      <c r="L60" s="69"/>
-      <c r="M60" s="69"/>
-      <c r="N60" s="69"/>
+      <c r="B60" s="55"/>
+      <c r="C60" s="55"/>
+      <c r="D60" s="55"/>
+      <c r="E60" s="55"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="55"/>
+      <c r="H60" s="55"/>
+      <c r="I60" s="55"/>
+      <c r="J60" s="55"/>
+      <c r="K60" s="55"/>
+      <c r="L60" s="55"/>
+      <c r="M60" s="55"/>
+      <c r="N60" s="55"/>
     </row>
     <row r="61" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="65" t="s">
+      <c r="A61" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B61" s="65"/>
-      <c r="C61" s="66" t="s">
+      <c r="B61" s="64"/>
+      <c r="C61" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="D61" s="66"/>
-      <c r="E61" s="66"/>
-      <c r="F61" s="66"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="61"/>
       <c r="G61" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H61" s="2"/>
-      <c r="I61" s="66" t="s">
+      <c r="I61" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="J61" s="66"/>
-      <c r="K61" s="66"/>
-      <c r="L61" s="66"/>
-      <c r="M61" s="66"/>
+      <c r="J61" s="61"/>
+      <c r="K61" s="61"/>
+      <c r="L61" s="61"/>
+      <c r="M61" s="61"/>
     </row>
     <row r="62" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="65" t="s">
+      <c r="A62" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B62" s="65"/>
-      <c r="C62" s="66" t="s">
+      <c r="B62" s="64"/>
+      <c r="C62" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="D62" s="66"/>
-      <c r="E62" s="66"/>
-      <c r="F62" s="66"/>
+      <c r="D62" s="61"/>
+      <c r="E62" s="61"/>
+      <c r="F62" s="61"/>
       <c r="G62" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H62" s="2"/>
-      <c r="I62" s="62" t="s">
+      <c r="I62" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="J62" s="62"/>
-      <c r="K62" s="62"/>
-      <c r="L62" s="62"/>
-      <c r="M62" s="62"/>
+      <c r="J62" s="51"/>
+      <c r="K62" s="51"/>
+      <c r="L62" s="51"/>
+      <c r="M62" s="51"/>
     </row>
     <row r="63" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="48" t="s">
+      <c r="A63" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B63" s="48"/>
-      <c r="C63" s="48"/>
-      <c r="D63" s="70" t="s">
+      <c r="B63" s="60"/>
+      <c r="C63" s="60"/>
+      <c r="D63" s="76" t="s">
         <v>43</v>
       </c>
-      <c r="E63" s="70"/>
-      <c r="F63" s="70"/>
-      <c r="G63" s="70"/>
-      <c r="H63" s="70"/>
-      <c r="I63" s="48" t="s">
+      <c r="E63" s="76"/>
+      <c r="F63" s="76"/>
+      <c r="G63" s="76"/>
+      <c r="H63" s="76"/>
+      <c r="I63" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="J63" s="48"/>
+      <c r="J63" s="60"/>
       <c r="K63" s="68" t="s">
         <v>54</v>
       </c>
@@ -4731,11 +4778,11 @@
       <c r="M63" s="68"/>
     </row>
     <row r="64" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="48" t="s">
+      <c r="A64" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B64" s="48"/>
-      <c r="C64" s="48"/>
+      <c r="B64" s="60"/>
+      <c r="C64" s="60"/>
       <c r="D64" s="68" t="s">
         <v>179</v>
       </c>
@@ -4743,10 +4790,10 @@
       <c r="F64" s="68"/>
       <c r="G64" s="68"/>
       <c r="H64" s="68"/>
-      <c r="I64" s="48" t="s">
+      <c r="I64" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="J64" s="48"/>
+      <c r="J64" s="60"/>
       <c r="K64" s="68">
         <v>1</v>
       </c>
@@ -4754,25 +4801,25 @@
       <c r="M64" s="68"/>
     </row>
     <row r="65" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="48" t="s">
+      <c r="A65" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="B65" s="48"/>
-      <c r="C65" s="48"/>
-      <c r="D65" s="67" t="s">
+      <c r="B65" s="60"/>
+      <c r="C65" s="60"/>
+      <c r="D65" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="E65" s="67"/>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
-      <c r="H65" s="67"/>
-      <c r="I65" s="67" t="s">
+      <c r="E65" s="75"/>
+      <c r="F65" s="75"/>
+      <c r="G65" s="75"/>
+      <c r="H65" s="75"/>
+      <c r="I65" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="J65" s="67"/>
-      <c r="K65" s="67"/>
-      <c r="L65" s="67"/>
-      <c r="M65" s="67"/>
+      <c r="J65" s="75"/>
+      <c r="K65" s="75"/>
+      <c r="L65" s="75"/>
+      <c r="M65" s="75"/>
     </row>
     <row r="66" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A66" s="68" t="s">
@@ -4841,28 +4888,28 @@
       <c r="A69" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B69" s="67" t="s">
+      <c r="B69" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="C69" s="67"/>
-      <c r="D69" s="67" t="s">
+      <c r="C69" s="75"/>
+      <c r="D69" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="48" t="s">
+      <c r="E69" s="75"/>
+      <c r="F69" s="75"/>
+      <c r="G69" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="H69" s="48"/>
-      <c r="I69" s="48" t="s">
+      <c r="H69" s="60"/>
+      <c r="I69" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="48"/>
-      <c r="K69" s="67" t="s">
+      <c r="J69" s="60"/>
+      <c r="K69" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="L69" s="67"/>
-      <c r="M69" s="67"/>
+      <c r="L69" s="75"/>
+      <c r="M69" s="75"/>
     </row>
     <row r="70" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="30" t="s">
@@ -4938,33 +4985,33 @@
       <c r="M72" s="68"/>
     </row>
     <row r="73" spans="1:13" ht="36" x14ac:dyDescent="0.2">
-      <c r="A73" s="48" t="s">
+      <c r="A73" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B73" s="48"/>
+      <c r="B73" s="60"/>
       <c r="C73" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D73" s="48" t="s">
+      <c r="D73" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="E73" s="48"/>
-      <c r="F73" s="67" t="s">
+      <c r="E73" s="60"/>
+      <c r="F73" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="G73" s="67"/>
-      <c r="H73" s="67" t="s">
+      <c r="G73" s="75"/>
+      <c r="H73" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="I73" s="67"/>
-      <c r="J73" s="67" t="s">
+      <c r="I73" s="75"/>
+      <c r="J73" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="K73" s="67"/>
-      <c r="L73" s="67" t="s">
+      <c r="K73" s="75"/>
+      <c r="L73" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="M73" s="67"/>
+      <c r="M73" s="75"/>
     </row>
     <row r="74" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="68" t="s">
@@ -4999,28 +5046,28 @@
       <c r="A75" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B75" s="67" t="s">
+      <c r="B75" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C75" s="67"/>
-      <c r="D75" s="67" t="s">
+      <c r="C75" s="75"/>
+      <c r="D75" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E75" s="67"/>
-      <c r="F75" s="48" t="s">
+      <c r="E75" s="75"/>
+      <c r="F75" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48" t="s">
+      <c r="G75" s="60"/>
+      <c r="H75" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="I75" s="48"/>
-      <c r="J75" s="48"/>
-      <c r="K75" s="67" t="s">
+      <c r="I75" s="60"/>
+      <c r="J75" s="60"/>
+      <c r="K75" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="L75" s="67"/>
-      <c r="M75" s="67"/>
+      <c r="L75" s="75"/>
+      <c r="M75" s="75"/>
     </row>
     <row r="76" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="30" t="s">
@@ -5096,31 +5143,31 @@
       <c r="M78" s="68"/>
     </row>
     <row r="79" spans="1:13" ht="18" x14ac:dyDescent="0.2">
-      <c r="A79" s="48" t="s">
+      <c r="A79" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B79" s="48"/>
-      <c r="C79" s="48"/>
-      <c r="D79" s="48" t="s">
+      <c r="B79" s="60"/>
+      <c r="C79" s="60"/>
+      <c r="D79" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48" t="s">
+      <c r="E79" s="60"/>
+      <c r="F79" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="G79" s="48"/>
-      <c r="H79" s="67" t="s">
+      <c r="G79" s="60"/>
+      <c r="H79" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="I79" s="67"/>
-      <c r="J79" s="67" t="s">
+      <c r="I79" s="75"/>
+      <c r="J79" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K79" s="67"/>
-      <c r="L79" s="67" t="s">
+      <c r="K79" s="75"/>
+      <c r="L79" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="M79" s="67"/>
+      <c r="M79" s="75"/>
     </row>
     <row r="80" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="68" t="s">
@@ -5153,28 +5200,28 @@
       <c r="A81" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B81" s="67" t="s">
+      <c r="B81" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="C81" s="67"/>
-      <c r="D81" s="67" t="s">
+      <c r="C81" s="75"/>
+      <c r="D81" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E81" s="67"/>
-      <c r="F81" s="48" t="s">
+      <c r="E81" s="75"/>
+      <c r="F81" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="G81" s="48"/>
-      <c r="H81" s="48" t="s">
+      <c r="G81" s="60"/>
+      <c r="H81" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="I81" s="48"/>
-      <c r="J81" s="48"/>
-      <c r="K81" s="67" t="s">
+      <c r="I81" s="60"/>
+      <c r="J81" s="60"/>
+      <c r="K81" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="L81" s="67"/>
-      <c r="M81" s="67"/>
+      <c r="L81" s="75"/>
+      <c r="M81" s="75"/>
     </row>
     <row r="82" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="30" t="s">
@@ -5250,33 +5297,33 @@
       <c r="M84" s="68"/>
     </row>
     <row r="85" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="48" t="s">
+      <c r="A85" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B85" s="48"/>
+      <c r="B85" s="60"/>
       <c r="C85" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D85" s="48" t="s">
+      <c r="D85" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="E85" s="48"/>
-      <c r="F85" s="67" t="s">
+      <c r="E85" s="60"/>
+      <c r="F85" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="G85" s="67"/>
-      <c r="H85" s="67" t="s">
+      <c r="G85" s="75"/>
+      <c r="H85" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="I85" s="67"/>
-      <c r="J85" s="67" t="s">
+      <c r="I85" s="75"/>
+      <c r="J85" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="K85" s="67"/>
-      <c r="L85" s="67" t="s">
+      <c r="K85" s="75"/>
+      <c r="L85" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="M85" s="67"/>
+      <c r="M85" s="75"/>
     </row>
     <row r="86" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="68" t="s">
@@ -5329,60 +5376,60 @@
     </row>
     <row r="90" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="91" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="42" t="s">
+      <c r="A91" s="77" t="s">
         <v>202</v>
       </c>
-      <c r="B91" s="42"/>
-      <c r="C91" s="42"/>
-      <c r="D91" s="42"/>
-      <c r="E91" s="42"/>
-      <c r="F91" s="42"/>
-      <c r="G91" s="42"/>
-      <c r="H91" s="42"/>
-      <c r="I91" s="42"/>
-      <c r="J91" s="42"/>
-      <c r="K91" s="42"/>
-      <c r="L91" s="42"/>
-      <c r="M91" s="42"/>
+      <c r="B91" s="77"/>
+      <c r="C91" s="77"/>
+      <c r="D91" s="77"/>
+      <c r="E91" s="77"/>
+      <c r="F91" s="77"/>
+      <c r="G91" s="77"/>
+      <c r="H91" s="77"/>
+      <c r="I91" s="77"/>
+      <c r="J91" s="77"/>
+      <c r="K91" s="77"/>
+      <c r="L91" s="77"/>
+      <c r="M91" s="77"/>
     </row>
     <row r="92" spans="1:14" ht="378" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="42"/>
-      <c r="B92" s="42"/>
-      <c r="C92" s="42"/>
-      <c r="D92" s="42"/>
-      <c r="E92" s="42"/>
-      <c r="F92" s="42"/>
-      <c r="G92" s="42"/>
-      <c r="H92" s="42"/>
-      <c r="I92" s="42"/>
-      <c r="J92" s="42"/>
-      <c r="K92" s="42"/>
-      <c r="L92" s="42"/>
-      <c r="M92" s="42"/>
+      <c r="A92" s="77"/>
+      <c r="B92" s="77"/>
+      <c r="C92" s="77"/>
+      <c r="D92" s="77"/>
+      <c r="E92" s="77"/>
+      <c r="F92" s="77"/>
+      <c r="G92" s="77"/>
+      <c r="H92" s="77"/>
+      <c r="I92" s="77"/>
+      <c r="J92" s="77"/>
+      <c r="K92" s="77"/>
+      <c r="L92" s="77"/>
+      <c r="M92" s="77"/>
     </row>
     <row r="94" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="69" t="s">
+      <c r="A94" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B94" s="69"/>
-      <c r="C94" s="69"/>
-      <c r="D94" s="69"/>
-      <c r="E94" s="69"/>
-      <c r="F94" s="69"/>
-      <c r="G94" s="69"/>
-      <c r="H94" s="69"/>
-      <c r="I94" s="69"/>
-      <c r="J94" s="69"/>
-      <c r="K94" s="69"/>
-      <c r="L94" s="69"/>
-      <c r="M94" s="69"/>
-      <c r="N94" s="69"/>
+      <c r="B94" s="55"/>
+      <c r="C94" s="55"/>
+      <c r="D94" s="55"/>
+      <c r="E94" s="55"/>
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="55"/>
+      <c r="I94" s="55"/>
+      <c r="J94" s="55"/>
+      <c r="K94" s="55"/>
+      <c r="L94" s="55"/>
+      <c r="M94" s="55"/>
+      <c r="N94" s="55"/>
     </row>
     <row r="95" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="73" t="s">
+      <c r="A95" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B95" s="73"/>
+      <c r="B95" s="81"/>
       <c r="C95" s="68" t="s">
         <v>55</v>
       </c>
@@ -5400,13 +5447,13 @@
       <c r="K95" s="68"/>
       <c r="L95" s="68"/>
       <c r="M95" s="68"/>
-      <c r="N95" s="36"/>
+      <c r="N95" s="34"/>
     </row>
     <row r="96" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="73" t="s">
+      <c r="A96" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B96" s="73"/>
+      <c r="B96" s="81"/>
       <c r="C96" s="68" t="s">
         <v>57</v>
       </c>
@@ -5424,7 +5471,7 @@
       <c r="K96" s="68"/>
       <c r="L96" s="68"/>
       <c r="M96" s="68"/>
-      <c r="N96" s="36"/>
+      <c r="N96" s="34"/>
     </row>
     <row r="97" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="29"/>
@@ -5442,13 +5489,13 @@
       <c r="M97" s="28"/>
     </row>
     <row r="98" spans="1:13" ht="72" x14ac:dyDescent="0.2">
-      <c r="A98" s="37" t="s">
+      <c r="A98" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="B98" s="37" t="s">
+      <c r="B98" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="C98" s="37" t="s">
+      <c r="C98" s="35" t="s">
         <v>208</v>
       </c>
       <c r="D98" s="31" t="s">
@@ -5483,32 +5530,270 @@
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A99" s="38"/>
-      <c r="B99" s="36"/>
-      <c r="C99" s="36"/>
-      <c r="D99" s="36"/>
-      <c r="E99" s="36"/>
-      <c r="F99" s="36"/>
-      <c r="G99" s="36"/>
-      <c r="H99" s="36"/>
-      <c r="I99" s="36"/>
-      <c r="J99" s="36"/>
-      <c r="K99" s="36"/>
-      <c r="L99" s="36"/>
-      <c r="M99" s="36"/>
+      <c r="A99" s="36"/>
+      <c r="B99" s="34"/>
+      <c r="C99" s="34"/>
+      <c r="D99" s="34"/>
+      <c r="E99" s="34"/>
+      <c r="F99" s="34"/>
+      <c r="G99" s="34"/>
+      <c r="H99" s="34"/>
+      <c r="I99" s="34"/>
+      <c r="J99" s="34"/>
+      <c r="K99" s="34"/>
+      <c r="L99" s="34"/>
+      <c r="M99" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="282">
-    <mergeCell ref="L85:M85"/>
-    <mergeCell ref="L86:M86"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A91:M92"/>
+    <mergeCell ref="A94:N94"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="L73:M73"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="D67:H67"/>
+    <mergeCell ref="D68:H68"/>
+    <mergeCell ref="I67:M67"/>
+    <mergeCell ref="I68:M68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="I70:J72"/>
+    <mergeCell ref="K69:M69"/>
+    <mergeCell ref="K70:M72"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A60:N60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="I61:M61"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="I62:M62"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="I66:M66"/>
+    <mergeCell ref="D63:H63"/>
+    <mergeCell ref="D64:H64"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K63:M63"/>
+    <mergeCell ref="K64:M64"/>
+    <mergeCell ref="D65:H65"/>
+    <mergeCell ref="I65:M65"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A56:M57"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="J48:K50"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="D39:M39"/>
+    <mergeCell ref="D40:M40"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="L42:M44"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I42:K44"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="D38:M38"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="K23:M25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J25"/>
+    <mergeCell ref="K8:M10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="I17:M17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="I18:M18"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:F95"/>
+    <mergeCell ref="I95:M95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:F96"/>
+    <mergeCell ref="I96:M96"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A31:N31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="I32:M32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="I33:M33"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="D37:M37"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="L48:M50"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="K75:M75"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="H76:J78"/>
+    <mergeCell ref="D74:E74"/>
     <mergeCell ref="K76:M78"/>
     <mergeCell ref="D81:E81"/>
     <mergeCell ref="D82:E82"/>
@@ -5533,254 +5818,16 @@
     <mergeCell ref="L79:M79"/>
     <mergeCell ref="L80:M80"/>
     <mergeCell ref="D76:E76"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="H75:J75"/>
-    <mergeCell ref="H76:J78"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="K75:M75"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="L48:M50"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="D37:M37"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A28:M28"/>
-    <mergeCell ref="A31:N31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="I32:M32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="I33:M33"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="C95:F95"/>
-    <mergeCell ref="I95:M95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:F96"/>
-    <mergeCell ref="I96:M96"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="K8:M10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="A16:N16"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="I17:M17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="I18:M18"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="K23:M25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J25"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="D39:M39"/>
-    <mergeCell ref="D40:M40"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="L42:M44"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I42:K44"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="D38:M38"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A56:M57"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="J48:K50"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A60:N60"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="I61:M61"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="I62:M62"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="I66:M66"/>
-    <mergeCell ref="D63:H63"/>
-    <mergeCell ref="D64:H64"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="K63:M63"/>
-    <mergeCell ref="K64:M64"/>
-    <mergeCell ref="D65:H65"/>
-    <mergeCell ref="I65:M65"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="D67:H67"/>
-    <mergeCell ref="D68:H68"/>
-    <mergeCell ref="I67:M67"/>
-    <mergeCell ref="I68:M68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="I69:J69"/>
-    <mergeCell ref="I70:J72"/>
-    <mergeCell ref="K69:M69"/>
-    <mergeCell ref="K70:M72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A91:M92"/>
-    <mergeCell ref="A94:N94"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="G72:H72"/>
-    <mergeCell ref="L73:M73"/>
-    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="L85:M85"/>
+    <mergeCell ref="L86:M86"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="J86:K86"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5799,45 +5846,44 @@
   <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.125" style="16" customWidth="1"/>
-    <col min="2" max="2" width="7.75" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="6.75" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="6.125" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="16" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="7.5" customWidth="1"/>
+    <col min="4" max="4" width="6.625" customWidth="1"/>
+    <col min="5" max="5" width="7.5" customWidth="1"/>
+    <col min="6" max="6" width="6.625" customWidth="1"/>
+    <col min="7" max="7" width="7.5" customWidth="1"/>
     <col min="8" max="8" width="6.125" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="9" max="9" width="7" customWidth="1"/>
     <col min="10" max="10" width="5.875" customWidth="1"/>
     <col min="11" max="11" width="7.375" customWidth="1"/>
-    <col min="12" max="12" width="6.75" customWidth="1"/>
-    <col min="13" max="13" width="7.125" customWidth="1"/>
+    <col min="12" max="13" width="7.125" customWidth="1"/>
     <col min="14" max="14" width="0.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="55" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
     </row>
     <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="73"/>
+      <c r="B2" s="81"/>
       <c r="C2" s="68" t="s">
         <v>55</v>
       </c>
@@ -5855,13 +5901,13 @@
       <c r="K2" s="68"/>
       <c r="L2" s="68"/>
       <c r="M2" s="68"/>
-      <c r="N2" s="36"/>
+      <c r="N2" s="37"/>
     </row>
     <row r="3" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="73"/>
+      <c r="B3" s="81"/>
       <c r="C3" s="68" t="s">
         <v>57</v>
       </c>
@@ -5879,214 +5925,207 @@
       <c r="K3" s="68"/>
       <c r="L3" s="68"/>
       <c r="M3" s="68"/>
-      <c r="N3" s="36"/>
+      <c r="N3" s="37"/>
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="75" t="s">
         <v>221</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="40" t="s">
+      <c r="B4" s="75"/>
+      <c r="C4" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="F4" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="H4" s="40" t="s">
-        <v>229</v>
-      </c>
-      <c r="I4" s="40" t="s">
+      <c r="H4" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="I4" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="J4" s="41" t="s">
+      <c r="J4" s="39" t="s">
         <v>223</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="K4" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="L4" s="40" t="s">
+      <c r="L4" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="M4" s="76"/>
-      <c r="N4" s="39"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="84" t="s">
         <v>246</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="83"/>
+      <c r="C5" s="40" t="s">
         <v>234</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="40" t="s">
         <v>236</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="40" t="s">
         <v>239</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="40" t="s">
         <v>242</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="40" t="s">
         <v>241</v>
       </c>
-      <c r="M5" s="76"/>
-      <c r="N5" s="39"/>
+      <c r="M5" s="82"/>
+      <c r="N5" s="37"/>
     </row>
     <row r="6" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="75" t="s">
         <v>232</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="48" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="60" t="s">
         <v>247</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48" t="s">
+      <c r="D6" s="60"/>
+      <c r="E6" s="60" t="s">
         <v>226</v>
       </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48" t="s">
+      <c r="F6" s="60"/>
+      <c r="G6" s="60" t="s">
         <v>230</v>
       </c>
-      <c r="H6" s="48"/>
+      <c r="H6" s="60"/>
       <c r="I6" s="68"/>
       <c r="J6" s="68"/>
       <c r="K6" s="68"/>
       <c r="L6" s="68"/>
       <c r="M6" s="68"/>
-      <c r="N6" s="39"/>
+      <c r="N6" s="37"/>
     </row>
     <row r="7" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="84" t="s">
         <v>245</v>
       </c>
-      <c r="B7" s="78"/>
-      <c r="C7" s="68" t="s">
+      <c r="B7" s="83"/>
+      <c r="C7" s="83" t="s">
         <v>248</v>
       </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68" t="s">
+      <c r="D7" s="83"/>
+      <c r="E7" s="83" t="s">
         <v>249</v>
       </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68" t="s">
+      <c r="F7" s="83"/>
+      <c r="G7" s="83" t="s">
         <v>233</v>
       </c>
-      <c r="H7" s="68"/>
+      <c r="H7" s="83"/>
       <c r="I7" s="68"/>
       <c r="J7" s="68"/>
       <c r="K7" s="68"/>
       <c r="L7" s="68"/>
       <c r="M7" s="68"/>
-      <c r="N7" s="39"/>
+      <c r="N7" s="37"/>
     </row>
     <row r="8" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="58" t="s">
         <v>244</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="59"/>
     </row>
     <row r="9" spans="1:14" ht="72" x14ac:dyDescent="0.2">
-      <c r="A9" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="B9" s="37" t="s">
+      <c r="A9" s="42" t="s">
+        <v>252</v>
+      </c>
+      <c r="B9" s="42" t="s">
         <v>207</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="E9" s="33" t="s">
+      <c r="D9" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="E9" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="I9" s="33" t="s">
+      <c r="I9" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J9" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="K9" s="32" t="s">
+      <c r="K9" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="L9" s="33" t="s">
+      <c r="L9" s="42" t="s">
         <v>216</v>
       </c>
-      <c r="M9" s="33" t="s">
+      <c r="M9" s="42" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="38"/>
-      <c r="B10" s="79"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="47"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="I3:M3"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="C6:D6"/>
@@ -6100,19 +6139,16 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="I6:M7"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D9E8CF-1189-4035-9E4B-A80C090AA03D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/rpt_template.xlsx
+++ b/rpt_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\ZhuhaiZg\zkc1601\Resource\report_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FEEC3E-7DF2-465E-9559-1D0B1B4BC22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA2F06E-B8F2-4CDD-997A-71F7252B0E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{8C9C76BE-07CF-46C5-B8D9-D7207282EA5E}"/>
   </bookViews>
@@ -1378,14 +1378,65 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1396,89 +1447,38 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1819,23 +1819,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="64"/>
+      <c r="B2" s="71"/>
       <c r="C2" s="3" t="s">
         <v>55</v>
       </c>
@@ -1843,17 +1843,17 @@
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="64"/>
+      <c r="B3" s="71"/>
       <c r="C3" s="3" t="s">
         <v>57</v>
       </c>
@@ -1861,11 +1861,11 @@
       <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
     </row>
     <row r="4" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
@@ -1878,49 +1878,49 @@
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="52" t="s">
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="53"/>
+      <c r="E5" s="70"/>
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="68"/>
+      <c r="H5" s="74"/>
     </row>
     <row r="6" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="48" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="49" t="s">
         <v>176</v>
       </c>
       <c r="E6" s="50"/>
       <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="68">
+      <c r="G6" s="74">
         <v>1</v>
       </c>
-      <c r="H6" s="68"/>
+      <c r="H6" s="74"/>
     </row>
     <row r="7" spans="1:9" ht="36" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="57"/>
+      <c r="C7" s="56"/>
       <c r="D7" s="9" t="s">
         <v>34</v>
       </c>
@@ -1930,16 +1930,16 @@
       <c r="F7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="75" t="s">
+      <c r="G7" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="75"/>
+      <c r="H7" s="73"/>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="49" t="s">
         <v>59</v>
       </c>
       <c r="C8" s="50"/>
@@ -1949,19 +1949,19 @@
       <c r="E8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="68" t="s">
+      <c r="F8" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="G8" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="68"/>
+      <c r="H8" s="74"/>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="49" t="s">
         <v>64</v>
       </c>
       <c r="C9" s="50"/>
@@ -1971,15 +1971,15 @@
       <c r="E9" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="49" t="s">
         <v>67</v>
       </c>
       <c r="C10" s="50"/>
@@ -1989,61 +1989,61 @@
       <c r="E10" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
     </row>
     <row r="11" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="22"/>
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="60"/>
+      <c r="C11" s="54"/>
       <c r="D11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="75"/>
+      <c r="G11" s="73"/>
       <c r="H11" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="74" t="s">
         <v>194</v>
       </c>
-      <c r="C12" s="68"/>
+      <c r="C12" s="74"/>
       <c r="D12" s="6" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="G12" s="68"/>
+      <c r="G12" s="74"/>
       <c r="H12" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="394.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="77" t="s">
         <v>200</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="D14" s="1"/>
@@ -2063,23 +2063,23 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="55" t="s">
+      <c r="A17" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="75"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="75"/>
     </row>
     <row r="18" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="64"/>
+      <c r="B18" s="71"/>
       <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
@@ -2087,17 +2087,17 @@
       <c r="E18" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F18" s="61" t="s">
+      <c r="F18" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
     </row>
     <row r="19" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="64"/>
+      <c r="B19" s="71"/>
       <c r="C19" s="3" t="s">
         <v>57</v>
       </c>
@@ -2105,11 +2105,11 @@
       <c r="E19" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F19" s="51" t="s">
+      <c r="F19" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
     </row>
     <row r="20" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15"/>
@@ -2122,11 +2122,11 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="76" t="s">
         <v>22</v>
       </c>
@@ -2140,15 +2140,15 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="68" t="s">
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="74" t="s">
         <v>177</v>
       </c>
-      <c r="E22" s="68"/>
+      <c r="E22" s="74"/>
       <c r="F22" s="5" t="s">
         <v>13</v>
       </c>
@@ -2161,10 +2161,10 @@
       <c r="A23" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="73"/>
       <c r="D23" s="9" t="s">
         <v>18</v>
       </c>
@@ -2174,68 +2174,68 @@
       <c r="F23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="75" t="s">
+      <c r="G23" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="H23" s="75"/>
+      <c r="H23" s="73"/>
     </row>
     <row r="24" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="B24" s="68" t="s">
+      <c r="B24" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="68"/>
+      <c r="C24" s="74"/>
       <c r="D24" s="6" t="s">
         <v>75</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F24" s="68" t="s">
+      <c r="F24" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="G24" s="68" t="s">
+      <c r="G24" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="H24" s="68"/>
+      <c r="H24" s="74"/>
     </row>
     <row r="25" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="68"/>
+      <c r="C25" s="74"/>
       <c r="D25" s="6" t="s">
         <v>80</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F25" s="68"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="B26" s="68" t="s">
+      <c r="B26" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="68"/>
+      <c r="C26" s="74"/>
       <c r="D26" s="6" t="s">
         <v>83</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="F26" s="68"/>
-      <c r="G26" s="68"/>
-      <c r="H26" s="68"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
     </row>
     <row r="27" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
@@ -2286,16 +2286,16 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="397.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="54" t="s">
+      <c r="A29" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="77"/>
+      <c r="E29" s="77"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="D30" s="1"/>
@@ -2315,23 +2315,23 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="55"/>
+      <c r="B33" s="75"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="75"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+      <c r="I33" s="75"/>
     </row>
     <row r="34" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="64" t="s">
+      <c r="A34" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="64"/>
+      <c r="B34" s="71"/>
       <c r="C34" s="3" t="s">
         <v>55</v>
       </c>
@@ -2339,17 +2339,17 @@
       <c r="E34" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F34" s="61" t="s">
+      <c r="F34" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
     </row>
     <row r="35" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="64" t="s">
+      <c r="A35" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B35" s="64"/>
+      <c r="B35" s="71"/>
       <c r="C35" s="3" t="s">
         <v>57</v>
       </c>
@@ -2357,11 +2357,11 @@
       <c r="E35" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F35" s="51" t="s">
+      <c r="F35" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="68"/>
     </row>
     <row r="36" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="15"/>
@@ -2374,15 +2374,15 @@
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="60" t="s">
+      <c r="A37" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="60"/>
-      <c r="C37" s="60"/>
-      <c r="D37" s="52" t="s">
+      <c r="B37" s="54"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="E37" s="53"/>
+      <c r="E37" s="70"/>
       <c r="F37" s="5" t="s">
         <v>12</v>
       </c>
@@ -2392,12 +2392,12 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="60" t="s">
+      <c r="A38" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="60"/>
-      <c r="C38" s="60"/>
-      <c r="D38" s="48" t="s">
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="49" t="s">
         <v>178</v>
       </c>
       <c r="E38" s="50"/>
@@ -2410,79 +2410,79 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="58" t="s">
+      <c r="A39" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="62"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="56" t="s">
+      <c r="B39" s="66"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="E39" s="63"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="57"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="56"/>
     </row>
     <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="48" t="s">
+      <c r="A40" s="49" t="s">
         <v>187</v>
       </c>
-      <c r="B40" s="49"/>
+      <c r="B40" s="53"/>
       <c r="C40" s="50"/>
-      <c r="D40" s="48" t="s">
+      <c r="D40" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
-      <c r="G40" s="49"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
       <c r="H40" s="50"/>
     </row>
     <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="48" t="s">
+      <c r="A41" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="B41" s="49"/>
+      <c r="B41" s="53"/>
       <c r="C41" s="50"/>
-      <c r="D41" s="48" t="s">
+      <c r="D41" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="E41" s="49"/>
-      <c r="F41" s="49"/>
-      <c r="G41" s="49"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53"/>
       <c r="H41" s="50"/>
     </row>
     <row r="42" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="48" t="s">
+      <c r="A42" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="B42" s="49"/>
+      <c r="B42" s="53"/>
       <c r="C42" s="50"/>
-      <c r="D42" s="48" t="s">
+      <c r="D42" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="49"/>
-      <c r="F42" s="49"/>
-      <c r="G42" s="49"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
       <c r="H42" s="50"/>
     </row>
     <row r="43" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B43" s="56" t="s">
+      <c r="B43" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="57"/>
+      <c r="C43" s="56"/>
       <c r="D43" s="9" t="s">
         <v>34</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F43" s="58" t="s">
+      <c r="F43" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G43" s="59"/>
+      <c r="G43" s="52"/>
       <c r="H43" s="9" t="s">
         <v>19</v>
       </c>
@@ -2491,7 +2491,7 @@
       <c r="A44" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="B44" s="48" t="s">
+      <c r="B44" s="49" t="s">
         <v>92</v>
       </c>
       <c r="C44" s="50"/>
@@ -2501,11 +2501,11 @@
       <c r="E44" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F44" s="69" t="s">
+      <c r="F44" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="G44" s="70"/>
-      <c r="H44" s="65" t="s">
+      <c r="G44" s="61"/>
+      <c r="H44" s="57" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       <c r="A45" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="B45" s="48" t="s">
+      <c r="B45" s="49" t="s">
         <v>97</v>
       </c>
       <c r="C45" s="50"/>
@@ -2523,15 +2523,15 @@
       <c r="E45" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F45" s="71"/>
-      <c r="G45" s="72"/>
-      <c r="H45" s="66"/>
+      <c r="F45" s="62"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="58"/>
     </row>
     <row r="46" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="B46" s="48" t="s">
+      <c r="B46" s="49" t="s">
         <v>100</v>
       </c>
       <c r="C46" s="50"/>
@@ -2541,16 +2541,16 @@
       <c r="E46" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F46" s="73"/>
-      <c r="G46" s="74"/>
-      <c r="H46" s="67"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="65"/>
+      <c r="H46" s="59"/>
     </row>
     <row r="47" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="60" t="s">
+      <c r="A47" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="B47" s="60"/>
-      <c r="C47" s="60"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
       <c r="D47" s="5" t="s">
         <v>10</v>
       </c>
@@ -2568,10 +2568,10 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="48" t="s">
+      <c r="A48" s="49" t="s">
         <v>195</v>
       </c>
-      <c r="B48" s="49"/>
+      <c r="B48" s="53"/>
       <c r="C48" s="50"/>
       <c r="D48" s="6" t="s">
         <v>103</v>
@@ -2593,20 +2593,20 @@
       <c r="A49" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B49" s="56" t="s">
+      <c r="B49" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="C49" s="57"/>
+      <c r="C49" s="56"/>
       <c r="D49" s="9" t="s">
         <v>34</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F49" s="58" t="s">
+      <c r="F49" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="59"/>
+      <c r="G49" s="52"/>
       <c r="H49" s="9" t="s">
         <v>24</v>
       </c>
@@ -2615,7 +2615,7 @@
       <c r="A50" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="B50" s="48" t="s">
+      <c r="B50" s="49" t="s">
         <v>108</v>
       </c>
       <c r="C50" s="50"/>
@@ -2625,11 +2625,11 @@
       <c r="E50" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F50" s="69" t="s">
+      <c r="F50" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="G50" s="70"/>
-      <c r="H50" s="65" t="s">
+      <c r="G50" s="61"/>
+      <c r="H50" s="57" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       <c r="A51" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="B51" s="48" t="s">
+      <c r="B51" s="49" t="s">
         <v>113</v>
       </c>
       <c r="C51" s="50"/>
@@ -2647,15 +2647,15 @@
       <c r="E51" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="F51" s="71"/>
-      <c r="G51" s="72"/>
-      <c r="H51" s="66"/>
+      <c r="F51" s="62"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="58"/>
     </row>
     <row r="52" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="B52" s="48" t="s">
+      <c r="B52" s="49" t="s">
         <v>116</v>
       </c>
       <c r="C52" s="50"/>
@@ -2665,15 +2665,15 @@
       <c r="E52" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="F52" s="73"/>
-      <c r="G52" s="74"/>
-      <c r="H52" s="67"/>
+      <c r="F52" s="64"/>
+      <c r="G52" s="65"/>
+      <c r="H52" s="59"/>
     </row>
     <row r="53" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="58" t="s">
+      <c r="A53" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B53" s="59"/>
+      <c r="B53" s="52"/>
       <c r="C53" s="9" t="s">
         <v>26</v>
       </c>
@@ -2694,10 +2694,10 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="48" t="s">
+      <c r="A54" s="49" t="s">
         <v>196</v>
       </c>
-      <c r="B54" s="49"/>
+      <c r="B54" s="53"/>
       <c r="C54" s="6" t="s">
         <v>39</v>
       </c>
@@ -2735,45 +2735,45 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="77" t="s">
+      <c r="A58" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="B58" s="77"/>
-      <c r="C58" s="77"/>
-      <c r="D58" s="77"/>
-      <c r="E58" s="77"/>
-      <c r="F58" s="77"/>
-      <c r="G58" s="77"/>
-      <c r="H58" s="77"/>
+      <c r="B58" s="48"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="48"/>
     </row>
     <row r="59" spans="1:9" ht="386.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="77"/>
-      <c r="B59" s="77"/>
-      <c r="C59" s="77"/>
-      <c r="D59" s="77"/>
-      <c r="E59" s="77"/>
-      <c r="F59" s="77"/>
-      <c r="G59" s="77"/>
-      <c r="H59" s="77"/>
+      <c r="A59" s="48"/>
+      <c r="B59" s="48"/>
+      <c r="C59" s="48"/>
+      <c r="D59" s="48"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
     </row>
     <row r="62" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="55" t="s">
+      <c r="A62" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B62" s="55"/>
-      <c r="C62" s="55"/>
-      <c r="D62" s="55"/>
-      <c r="E62" s="55"/>
-      <c r="F62" s="55"/>
-      <c r="G62" s="55"/>
-      <c r="H62" s="55"/>
-      <c r="I62" s="55"/>
+      <c r="B62" s="75"/>
+      <c r="C62" s="75"/>
+      <c r="D62" s="75"/>
+      <c r="E62" s="75"/>
+      <c r="F62" s="75"/>
+      <c r="G62" s="75"/>
+      <c r="H62" s="75"/>
+      <c r="I62" s="75"/>
     </row>
     <row r="63" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="64" t="s">
+      <c r="A63" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B63" s="64"/>
+      <c r="B63" s="71"/>
       <c r="C63" s="3" t="s">
         <v>55</v>
       </c>
@@ -2781,17 +2781,17 @@
       <c r="E63" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F63" s="61" t="s">
+      <c r="F63" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="G63" s="61"/>
-      <c r="H63" s="61"/>
+      <c r="G63" s="72"/>
+      <c r="H63" s="72"/>
     </row>
     <row r="64" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="64" t="s">
+      <c r="A64" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B64" s="64"/>
+      <c r="B64" s="71"/>
       <c r="C64" s="3" t="s">
         <v>57</v>
       </c>
@@ -2799,11 +2799,11 @@
       <c r="E64" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F64" s="51" t="s">
+      <c r="F64" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="G64" s="51"/>
-      <c r="H64" s="51"/>
+      <c r="G64" s="68"/>
+      <c r="H64" s="68"/>
     </row>
     <row r="65" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="15"/>
@@ -2816,15 +2816,15 @@
       <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="60" t="s">
+      <c r="A66" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B66" s="60"/>
-      <c r="C66" s="60"/>
-      <c r="D66" s="52" t="s">
+      <c r="B66" s="54"/>
+      <c r="C66" s="54"/>
+      <c r="D66" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="E66" s="53"/>
+      <c r="E66" s="70"/>
       <c r="F66" s="5" t="s">
         <v>12</v>
       </c>
@@ -2834,12 +2834,12 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="60" t="s">
+      <c r="A67" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B67" s="60"/>
-      <c r="C67" s="60"/>
-      <c r="D67" s="48" t="s">
+      <c r="B67" s="54"/>
+      <c r="C67" s="54"/>
+      <c r="D67" s="49" t="s">
         <v>179</v>
       </c>
       <c r="E67" s="50"/>
@@ -2852,65 +2852,65 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="18" x14ac:dyDescent="0.2">
-      <c r="A68" s="58" t="s">
+      <c r="A68" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B68" s="62"/>
-      <c r="C68" s="59"/>
-      <c r="D68" s="56" t="s">
+      <c r="B68" s="66"/>
+      <c r="C68" s="52"/>
+      <c r="D68" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="E68" s="63"/>
-      <c r="F68" s="63"/>
-      <c r="G68" s="63" t="s">
+      <c r="E68" s="67"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="H68" s="57"/>
+      <c r="H68" s="56"/>
     </row>
     <row r="69" spans="1:8" ht="18" x14ac:dyDescent="0.2">
-      <c r="A69" s="48" t="s">
+      <c r="A69" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="B69" s="49"/>
+      <c r="B69" s="53"/>
       <c r="C69" s="50"/>
-      <c r="D69" s="48" t="s">
+      <c r="D69" s="49" t="s">
         <v>124</v>
       </c>
-      <c r="E69" s="49"/>
-      <c r="F69" s="49"/>
-      <c r="G69" s="49" t="s">
+      <c r="E69" s="53"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53" t="s">
         <v>125</v>
       </c>
       <c r="H69" s="50"/>
     </row>
     <row r="70" spans="1:8" ht="18" x14ac:dyDescent="0.2">
-      <c r="A70" s="48" t="s">
+      <c r="A70" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="B70" s="49"/>
+      <c r="B70" s="53"/>
       <c r="C70" s="50"/>
-      <c r="D70" s="48" t="s">
+      <c r="D70" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="E70" s="49"/>
-      <c r="F70" s="49"/>
-      <c r="G70" s="49" t="s">
+      <c r="E70" s="53"/>
+      <c r="F70" s="53"/>
+      <c r="G70" s="53" t="s">
         <v>127</v>
       </c>
       <c r="H70" s="50"/>
     </row>
     <row r="71" spans="1:8" ht="18" x14ac:dyDescent="0.2">
-      <c r="A71" s="48" t="s">
+      <c r="A71" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="B71" s="49"/>
+      <c r="B71" s="53"/>
       <c r="C71" s="50"/>
-      <c r="D71" s="48" t="s">
+      <c r="D71" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="E71" s="49"/>
-      <c r="F71" s="49"/>
-      <c r="G71" s="49" t="s">
+      <c r="E71" s="53"/>
+      <c r="F71" s="53"/>
+      <c r="G71" s="53" t="s">
         <v>129</v>
       </c>
       <c r="H71" s="50"/>
@@ -2919,20 +2919,20 @@
       <c r="A72" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B72" s="56" t="s">
+      <c r="B72" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="C72" s="57"/>
+      <c r="C72" s="56"/>
       <c r="D72" s="14" t="s">
         <v>34</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F72" s="58" t="s">
+      <c r="F72" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="59"/>
+      <c r="G72" s="52"/>
       <c r="H72" s="14" t="s">
         <v>46</v>
       </c>
@@ -2941,7 +2941,7 @@
       <c r="A73" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B73" s="48" t="s">
+      <c r="B73" s="49" t="s">
         <v>130</v>
       </c>
       <c r="C73" s="50"/>
@@ -2951,11 +2951,11 @@
       <c r="E73" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F73" s="69" t="s">
+      <c r="F73" s="60" t="s">
         <v>133</v>
       </c>
-      <c r="G73" s="70"/>
-      <c r="H73" s="65" t="s">
+      <c r="G73" s="61"/>
+      <c r="H73" s="57" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       <c r="A74" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="B74" s="48" t="s">
+      <c r="B74" s="49" t="s">
         <v>135</v>
       </c>
       <c r="C74" s="50"/>
@@ -2973,15 +2973,15 @@
       <c r="E74" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="F74" s="71"/>
-      <c r="G74" s="72"/>
-      <c r="H74" s="66"/>
+      <c r="F74" s="62"/>
+      <c r="G74" s="63"/>
+      <c r="H74" s="58"/>
     </row>
     <row r="75" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B75" s="48" t="s">
+      <c r="B75" s="49" t="s">
         <v>138</v>
       </c>
       <c r="C75" s="50"/>
@@ -2991,15 +2991,15 @@
       <c r="E75" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="F75" s="73"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="67"/>
+      <c r="F75" s="64"/>
+      <c r="G75" s="65"/>
+      <c r="H75" s="59"/>
     </row>
     <row r="76" spans="1:8" ht="36" x14ac:dyDescent="0.2">
-      <c r="A76" s="58" t="s">
+      <c r="A76" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B76" s="59"/>
+      <c r="B76" s="52"/>
       <c r="C76" s="14" t="s">
         <v>26</v>
       </c>
@@ -3020,10 +3020,10 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="48" t="s">
+      <c r="A77" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B77" s="49"/>
+      <c r="B77" s="53"/>
       <c r="C77" s="13" t="s">
         <v>39</v>
       </c>
@@ -3047,20 +3047,20 @@
       <c r="A78" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B78" s="56" t="s">
+      <c r="B78" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="57"/>
+      <c r="C78" s="56"/>
       <c r="D78" s="14" t="s">
         <v>34</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F78" s="58" t="s">
+      <c r="F78" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G78" s="59"/>
+      <c r="G78" s="52"/>
       <c r="H78" s="14" t="s">
         <v>19</v>
       </c>
@@ -3069,7 +3069,7 @@
       <c r="A79" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B79" s="48" t="s">
+      <c r="B79" s="49" t="s">
         <v>146</v>
       </c>
       <c r="C79" s="50"/>
@@ -3079,11 +3079,11 @@
       <c r="E79" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F79" s="69" t="s">
+      <c r="F79" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="G79" s="70"/>
-      <c r="H79" s="65" t="s">
+      <c r="G79" s="61"/>
+      <c r="H79" s="57" t="s">
         <v>150</v>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       <c r="A80" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="B80" s="48" t="s">
+      <c r="B80" s="49" t="s">
         <v>151</v>
       </c>
       <c r="C80" s="50"/>
@@ -3101,15 +3101,15 @@
       <c r="E80" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="F80" s="71"/>
-      <c r="G80" s="72"/>
-      <c r="H80" s="66"/>
+      <c r="F80" s="62"/>
+      <c r="G80" s="63"/>
+      <c r="H80" s="58"/>
     </row>
     <row r="81" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B81" s="48" t="s">
+      <c r="B81" s="49" t="s">
         <v>154</v>
       </c>
       <c r="C81" s="50"/>
@@ -3119,16 +3119,16 @@
       <c r="E81" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="F81" s="73"/>
-      <c r="G81" s="74"/>
-      <c r="H81" s="67"/>
+      <c r="F81" s="64"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="59"/>
     </row>
     <row r="82" spans="1:9" ht="36" x14ac:dyDescent="0.2">
-      <c r="A82" s="60" t="s">
+      <c r="A82" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="B82" s="60"/>
-      <c r="C82" s="60"/>
+      <c r="B82" s="54"/>
+      <c r="C82" s="54"/>
       <c r="D82" s="5" t="s">
         <v>10</v>
       </c>
@@ -3146,10 +3146,10 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="48" t="s">
+      <c r="A83" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="B83" s="49"/>
+      <c r="B83" s="53"/>
       <c r="C83" s="50"/>
       <c r="D83" s="6" t="s">
         <v>157</v>
@@ -3171,20 +3171,20 @@
       <c r="A84" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B84" s="56" t="s">
+      <c r="B84" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="C84" s="57"/>
+      <c r="C84" s="56"/>
       <c r="D84" s="9" t="s">
         <v>34</v>
       </c>
       <c r="E84" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F84" s="58" t="s">
+      <c r="F84" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G84" s="59"/>
+      <c r="G84" s="52"/>
       <c r="H84" s="9" t="s">
         <v>24</v>
       </c>
@@ -3193,7 +3193,7 @@
       <c r="A85" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B85" s="48" t="s">
+      <c r="B85" s="49" t="s">
         <v>162</v>
       </c>
       <c r="C85" s="50"/>
@@ -3203,11 +3203,11 @@
       <c r="E85" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="F85" s="69" t="s">
+      <c r="F85" s="60" t="s">
         <v>165</v>
       </c>
-      <c r="G85" s="70"/>
-      <c r="H85" s="65" t="s">
+      <c r="G85" s="61"/>
+      <c r="H85" s="57" t="s">
         <v>166</v>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       <c r="A86" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="B86" s="48" t="s">
+      <c r="B86" s="49" t="s">
         <v>167</v>
       </c>
       <c r="C86" s="50"/>
@@ -3225,15 +3225,15 @@
       <c r="E86" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F86" s="71"/>
-      <c r="G86" s="72"/>
-      <c r="H86" s="66"/>
+      <c r="F86" s="62"/>
+      <c r="G86" s="63"/>
+      <c r="H86" s="58"/>
     </row>
     <row r="87" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B87" s="48" t="s">
+      <c r="B87" s="49" t="s">
         <v>170</v>
       </c>
       <c r="C87" s="50"/>
@@ -3243,15 +3243,15 @@
       <c r="E87" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="F87" s="73"/>
-      <c r="G87" s="74"/>
-      <c r="H87" s="67"/>
+      <c r="F87" s="64"/>
+      <c r="G87" s="65"/>
+      <c r="H87" s="59"/>
     </row>
     <row r="88" spans="1:9" ht="36" x14ac:dyDescent="0.2">
-      <c r="A88" s="58" t="s">
+      <c r="A88" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B88" s="59"/>
+      <c r="B88" s="52"/>
       <c r="C88" s="9" t="s">
         <v>26</v>
       </c>
@@ -3272,10 +3272,10 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="48" t="s">
+      <c r="A89" s="49" t="s">
         <v>199</v>
       </c>
-      <c r="B89" s="49"/>
+      <c r="B89" s="53"/>
       <c r="C89" s="6" t="s">
         <v>39</v>
       </c>
@@ -3315,85 +3315,74 @@
     </row>
     <row r="93" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="94" spans="1:9" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="77" t="s">
+      <c r="A94" s="48" t="s">
         <v>202</v>
       </c>
-      <c r="B94" s="77"/>
-      <c r="C94" s="77"/>
-      <c r="D94" s="77"/>
-      <c r="E94" s="77"/>
-      <c r="F94" s="77"/>
-      <c r="G94" s="77"/>
-      <c r="H94" s="77"/>
+      <c r="B94" s="48"/>
+      <c r="C94" s="48"/>
+      <c r="D94" s="48"/>
+      <c r="E94" s="48"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="48"/>
+      <c r="H94" s="48"/>
     </row>
     <row r="95" spans="1:9" ht="378" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="77"/>
-      <c r="B95" s="77"/>
-      <c r="C95" s="77"/>
-      <c r="D95" s="77"/>
-      <c r="E95" s="77"/>
-      <c r="F95" s="77"/>
-      <c r="G95" s="77"/>
-      <c r="H95" s="77"/>
+      <c r="A95" s="48"/>
+      <c r="B95" s="48"/>
+      <c r="C95" s="48"/>
+      <c r="D95" s="48"/>
+      <c r="E95" s="48"/>
+      <c r="F95" s="48"/>
+      <c r="G95" s="48"/>
+      <c r="H95" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="125">
-    <mergeCell ref="A94:H95"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="H85:H87"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G87"/>
-    <mergeCell ref="H79:H81"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="F73:G75"/>
-    <mergeCell ref="H73:H75"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="F79:G81"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A58:H59"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="F50:G52"/>
-    <mergeCell ref="H50:H52"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="H44:H46"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G46"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H26"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="G8:H10"/>
@@ -3418,51 +3407,62 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="H44:H46"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G46"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H26"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A58:H59"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="F50:G52"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="H79:H81"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="F73:G75"/>
+    <mergeCell ref="H73:H75"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="F79:G81"/>
+    <mergeCell ref="A94:H95"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="H85:H87"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3497,68 +3497,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
     </row>
     <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="61" t="s">
+      <c r="B2" s="71"/>
+      <c r="C2" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
       <c r="G2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="2"/>
-      <c r="I2" s="61" t="s">
+      <c r="I2" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
     </row>
     <row r="3" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="61" t="s">
+      <c r="B3" s="71"/>
+      <c r="C3" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
       <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="2"/>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
     </row>
     <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
@@ -3576,217 +3576,217 @@
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="52" t="s">
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="58" t="s">
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="59"/>
-      <c r="K5" s="68" t="s">
+      <c r="J5" s="52"/>
+      <c r="K5" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
     </row>
     <row r="6" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="48" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="49" t="s">
         <v>176</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
       <c r="H6" s="50"/>
-      <c r="I6" s="58" t="s">
+      <c r="I6" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="59"/>
-      <c r="K6" s="68">
+      <c r="J6" s="52"/>
+      <c r="K6" s="74">
         <v>1</v>
       </c>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
     </row>
     <row r="7" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="56" t="s">
+      <c r="C7" s="56"/>
+      <c r="D7" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="63"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="58" t="s">
+      <c r="E7" s="67"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="58" t="s">
+      <c r="H7" s="52"/>
+      <c r="I7" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="59"/>
-      <c r="K7" s="75" t="s">
+      <c r="J7" s="52"/>
+      <c r="K7" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="75"/>
-      <c r="M7" s="75"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
     </row>
     <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="49" t="s">
         <v>59</v>
       </c>
       <c r="C8" s="50"/>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="49"/>
+      <c r="E8" s="53"/>
       <c r="F8" s="50"/>
       <c r="G8" s="32" t="s">
         <v>61</v>
       </c>
       <c r="H8" s="33"/>
-      <c r="I8" s="69" t="s">
+      <c r="I8" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="70"/>
-      <c r="K8" s="68" t="s">
+      <c r="J8" s="61"/>
+      <c r="K8" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="74"/>
     </row>
     <row r="9" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="49" t="s">
         <v>64</v>
       </c>
       <c r="C9" s="50"/>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="49"/>
+      <c r="E9" s="53"/>
       <c r="F9" s="50"/>
       <c r="G9" s="32" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="33"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="68"/>
-      <c r="M9" s="68"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="74"/>
+      <c r="L9" s="74"/>
+      <c r="M9" s="74"/>
     </row>
     <row r="10" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="49" t="s">
         <v>67</v>
       </c>
       <c r="C10" s="50"/>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="49"/>
+      <c r="E10" s="53"/>
       <c r="F10" s="50"/>
       <c r="G10" s="32" t="s">
         <v>69</v>
       </c>
       <c r="H10" s="33"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="68"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="68"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="74"/>
+      <c r="M10" s="74"/>
     </row>
     <row r="11" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="22"/>
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="58" t="s">
+      <c r="C11" s="54"/>
+      <c r="D11" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="62"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="58" t="s">
+      <c r="E11" s="66"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="59"/>
-      <c r="I11" s="56" t="s">
+      <c r="H11" s="52"/>
+      <c r="I11" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="63"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="56" t="s">
+      <c r="J11" s="67"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="M11" s="57"/>
+      <c r="M11" s="56"/>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="74" t="s">
         <v>194</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="48" t="s">
+      <c r="C12" s="74"/>
+      <c r="D12" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="49"/>
+      <c r="E12" s="53"/>
       <c r="F12" s="50"/>
-      <c r="G12" s="48" t="s">
+      <c r="G12" s="49" t="s">
         <v>71</v>
       </c>
       <c r="H12" s="50"/>
-      <c r="I12" s="48" t="s">
+      <c r="I12" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="J12" s="49"/>
+      <c r="J12" s="53"/>
       <c r="K12" s="50"/>
-      <c r="L12" s="48" t="s">
+      <c r="L12" s="49" t="s">
         <v>73</v>
       </c>
       <c r="M12" s="50"/>
     </row>
     <row r="13" spans="1:14" ht="401.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="77" t="s">
         <v>200</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="54"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="54"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="77"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="F14" s="1"/>
@@ -3808,68 +3808,68 @@
       <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="55"/>
+      <c r="B16" s="75"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="75"/>
+      <c r="L16" s="75"/>
+      <c r="M16" s="75"/>
+      <c r="N16" s="75"/>
     </row>
     <row r="17" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="61" t="s">
+      <c r="B17" s="71"/>
+      <c r="C17" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="72"/>
       <c r="G17" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H17" s="2"/>
-      <c r="I17" s="61" t="s">
+      <c r="I17" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
-      <c r="L17" s="61"/>
-      <c r="M17" s="61"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="72"/>
+      <c r="M17" s="72"/>
     </row>
     <row r="18" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="61" t="s">
+      <c r="B18" s="71"/>
+      <c r="C18" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
       <c r="G18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="2"/>
-      <c r="I18" s="51" t="s">
+      <c r="I18" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="51"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="68"/>
+      <c r="M18" s="68"/>
     </row>
     <row r="19" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
@@ -3887,225 +3887,225 @@
       <c r="M19" s="4"/>
     </row>
     <row r="20" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="60" t="s">
+      <c r="A20" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="52" t="s">
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="58" t="s">
+      <c r="E20" s="78"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="J20" s="59"/>
-      <c r="K20" s="48" t="s">
+      <c r="J20" s="52"/>
+      <c r="K20" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="L20" s="49"/>
+      <c r="L20" s="53"/>
       <c r="M20" s="50"/>
     </row>
     <row r="21" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="48" t="s">
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="49" t="s">
         <v>177</v>
       </c>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
       <c r="H21" s="50"/>
-      <c r="I21" s="58" t="s">
+      <c r="I21" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="59"/>
-      <c r="K21" s="48">
+      <c r="J21" s="52"/>
+      <c r="K21" s="49">
         <v>1</v>
       </c>
-      <c r="L21" s="49"/>
+      <c r="L21" s="53"/>
       <c r="M21" s="50"/>
     </row>
     <row r="22" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="75"/>
-      <c r="D22" s="56" t="s">
+      <c r="C22" s="73"/>
+      <c r="D22" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="63"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="56" t="s">
+      <c r="E22" s="67"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="H22" s="57"/>
-      <c r="I22" s="56" t="s">
+      <c r="H22" s="56"/>
+      <c r="I22" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="J22" s="57"/>
-      <c r="K22" s="75" t="s">
+      <c r="J22" s="56"/>
+      <c r="K22" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="L22" s="75"/>
-      <c r="M22" s="75"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
     </row>
     <row r="23" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="B23" s="68" t="s">
+      <c r="B23" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="68"/>
-      <c r="D23" s="48" t="s">
+      <c r="C23" s="74"/>
+      <c r="D23" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="E23" s="49"/>
+      <c r="E23" s="53"/>
       <c r="F23" s="50"/>
-      <c r="G23" s="48" t="s">
+      <c r="G23" s="49" t="s">
         <v>76</v>
       </c>
       <c r="H23" s="50"/>
-      <c r="I23" s="69" t="s">
+      <c r="I23" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="J23" s="70"/>
-      <c r="K23" s="68" t="s">
+      <c r="J23" s="61"/>
+      <c r="K23" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="L23" s="68"/>
-      <c r="M23" s="68"/>
+      <c r="L23" s="74"/>
+      <c r="M23" s="74"/>
     </row>
     <row r="24" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B24" s="68" t="s">
+      <c r="B24" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="68"/>
-      <c r="D24" s="48" t="s">
+      <c r="C24" s="74"/>
+      <c r="D24" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="49"/>
+      <c r="E24" s="53"/>
       <c r="F24" s="50"/>
-      <c r="G24" s="48" t="s">
+      <c r="G24" s="49" t="s">
         <v>81</v>
       </c>
       <c r="H24" s="50"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="68"/>
-      <c r="M24" s="68"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="74"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="74"/>
     </row>
     <row r="25" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="48" t="s">
+      <c r="C25" s="74"/>
+      <c r="D25" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="49"/>
+      <c r="E25" s="53"/>
       <c r="F25" s="50"/>
-      <c r="G25" s="48" t="s">
+      <c r="G25" s="49" t="s">
         <v>84</v>
       </c>
       <c r="H25" s="50"/>
-      <c r="I25" s="73"/>
-      <c r="J25" s="74"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="74"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="74"/>
     </row>
     <row r="26" spans="1:14" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="57"/>
-      <c r="C26" s="56" t="s">
+      <c r="B26" s="56"/>
+      <c r="C26" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="57"/>
-      <c r="E26" s="56" t="s">
+      <c r="D26" s="56"/>
+      <c r="E26" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="57"/>
-      <c r="G26" s="56" t="s">
+      <c r="F26" s="56"/>
+      <c r="G26" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="H26" s="57"/>
-      <c r="I26" s="56" t="s">
+      <c r="H26" s="56"/>
+      <c r="I26" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="J26" s="57"/>
+      <c r="J26" s="56"/>
       <c r="K26" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="L26" s="56" t="s">
+      <c r="L26" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="M26" s="57"/>
+      <c r="M26" s="56"/>
     </row>
     <row r="27" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="49" t="s">
         <v>85</v>
       </c>
       <c r="B27" s="50"/>
-      <c r="C27" s="48" t="s">
+      <c r="C27" s="49" t="s">
         <v>86</v>
       </c>
       <c r="D27" s="50"/>
-      <c r="E27" s="48" t="s">
+      <c r="E27" s="49" t="s">
         <v>87</v>
       </c>
       <c r="F27" s="50"/>
-      <c r="G27" s="48" t="s">
+      <c r="G27" s="49" t="s">
         <v>88</v>
       </c>
       <c r="H27" s="50"/>
-      <c r="I27" s="48" t="s">
+      <c r="I27" s="49" t="s">
         <v>89</v>
       </c>
       <c r="J27" s="50"/>
       <c r="K27" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="L27" s="78" t="s">
+      <c r="L27" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="M27" s="79"/>
+      <c r="M27" s="81"/>
     </row>
     <row r="28" spans="1:14" ht="397.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="B28" s="54"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="54"/>
-      <c r="K28" s="54"/>
-      <c r="L28" s="54"/>
-      <c r="M28" s="54"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="77"/>
+      <c r="K28" s="77"/>
+      <c r="L28" s="77"/>
+      <c r="M28" s="77"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="F29" s="1"/>
@@ -4127,68 +4127,68 @@
       <c r="L30" s="1"/>
     </row>
     <row r="31" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="55"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="55"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="55"/>
-      <c r="M31" s="55"/>
-      <c r="N31" s="55"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="75"/>
+      <c r="M31" s="75"/>
+      <c r="N31" s="75"/>
     </row>
     <row r="32" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="64" t="s">
+      <c r="A32" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="64"/>
-      <c r="C32" s="61" t="s">
+      <c r="B32" s="71"/>
+      <c r="C32" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
       <c r="G32" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H32" s="2"/>
-      <c r="I32" s="61" t="s">
+      <c r="I32" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="61"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
     </row>
     <row r="33" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="64" t="s">
+      <c r="A33" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="64"/>
-      <c r="C33" s="61" t="s">
+      <c r="B33" s="71"/>
+      <c r="C33" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
       <c r="G33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H33" s="2"/>
-      <c r="I33" s="51" t="s">
+      <c r="I33" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="J33" s="51"/>
-      <c r="K33" s="51"/>
-      <c r="L33" s="51"/>
-      <c r="M33" s="51"/>
+      <c r="J33" s="68"/>
+      <c r="K33" s="68"/>
+      <c r="L33" s="68"/>
+      <c r="M33" s="68"/>
     </row>
     <row r="34" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="15"/>
@@ -4206,438 +4206,438 @@
       <c r="M34" s="4"/>
     </row>
     <row r="35" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="60" t="s">
+      <c r="A35" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="60"/>
-      <c r="C35" s="60"/>
-      <c r="D35" s="52" t="s">
+      <c r="B35" s="54"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="80"/>
-      <c r="F35" s="80"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="58" t="s">
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="J35" s="59"/>
-      <c r="K35" s="48" t="s">
+      <c r="J35" s="52"/>
+      <c r="K35" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="L35" s="49"/>
+      <c r="L35" s="53"/>
       <c r="M35" s="50"/>
     </row>
     <row r="36" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="60" t="s">
+      <c r="A36" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="60"/>
-      <c r="C36" s="60"/>
-      <c r="D36" s="48" t="s">
+      <c r="B36" s="54"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="49" t="s">
         <v>178</v>
       </c>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
       <c r="H36" s="50"/>
-      <c r="I36" s="58" t="s">
+      <c r="I36" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="J36" s="59"/>
-      <c r="K36" s="48">
+      <c r="J36" s="52"/>
+      <c r="K36" s="49">
         <v>1</v>
       </c>
-      <c r="L36" s="49"/>
+      <c r="L36" s="53"/>
       <c r="M36" s="50"/>
     </row>
     <row r="37" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="58" t="s">
+      <c r="A37" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="62"/>
-      <c r="C37" s="59"/>
-      <c r="D37" s="56" t="s">
+      <c r="B37" s="66"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="E37" s="63"/>
-      <c r="F37" s="63"/>
-      <c r="G37" s="63"/>
-      <c r="H37" s="63"/>
-      <c r="I37" s="63"/>
-      <c r="J37" s="63"/>
-      <c r="K37" s="63"/>
-      <c r="L37" s="63"/>
-      <c r="M37" s="57"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="67"/>
+      <c r="J37" s="67"/>
+      <c r="K37" s="67"/>
+      <c r="L37" s="67"/>
+      <c r="M37" s="56"/>
     </row>
     <row r="38" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="48" t="s">
+      <c r="A38" s="49" t="s">
         <v>187</v>
       </c>
-      <c r="B38" s="49"/>
+      <c r="B38" s="53"/>
       <c r="C38" s="50"/>
-      <c r="D38" s="48" t="s">
+      <c r="D38" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="49"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="53"/>
       <c r="M38" s="50"/>
     </row>
     <row r="39" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="48" t="s">
+      <c r="A39" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="B39" s="49"/>
+      <c r="B39" s="53"/>
       <c r="C39" s="50"/>
-      <c r="D39" s="48" t="s">
+      <c r="D39" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="49"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="53"/>
       <c r="M39" s="50"/>
     </row>
     <row r="40" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="48" t="s">
+      <c r="A40" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="B40" s="49"/>
+      <c r="B40" s="53"/>
       <c r="C40" s="50"/>
-      <c r="D40" s="48" t="s">
+      <c r="D40" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
-      <c r="G40" s="49"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="K40" s="49"/>
-      <c r="L40" s="49"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="53"/>
       <c r="M40" s="50"/>
     </row>
     <row r="41" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="56" t="s">
+      <c r="B41" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="C41" s="57"/>
-      <c r="D41" s="56" t="s">
+      <c r="C41" s="56"/>
+      <c r="D41" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="E41" s="57"/>
-      <c r="F41" s="58" t="s">
+      <c r="E41" s="56"/>
+      <c r="F41" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="G41" s="62"/>
-      <c r="H41" s="59"/>
-      <c r="I41" s="58" t="s">
+      <c r="G41" s="66"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="62"/>
-      <c r="K41" s="59"/>
-      <c r="L41" s="56" t="s">
+      <c r="J41" s="66"/>
+      <c r="K41" s="52"/>
+      <c r="L41" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="M41" s="57"/>
+      <c r="M41" s="56"/>
     </row>
     <row r="42" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="B42" s="48" t="s">
+      <c r="B42" s="49" t="s">
         <v>92</v>
       </c>
       <c r="C42" s="50"/>
-      <c r="D42" s="48" t="s">
+      <c r="D42" s="49" t="s">
         <v>93</v>
       </c>
       <c r="E42" s="50"/>
-      <c r="F42" s="68" t="s">
+      <c r="F42" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="G42" s="68"/>
-      <c r="H42" s="68"/>
-      <c r="I42" s="68" t="s">
+      <c r="G42" s="74"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="J42" s="68"/>
-      <c r="K42" s="68"/>
-      <c r="L42" s="68" t="s">
+      <c r="J42" s="74"/>
+      <c r="K42" s="74"/>
+      <c r="L42" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="M42" s="68"/>
+      <c r="M42" s="74"/>
     </row>
     <row r="43" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="B43" s="48" t="s">
+      <c r="B43" s="49" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="50"/>
-      <c r="D43" s="48" t="s">
+      <c r="D43" s="49" t="s">
         <v>98</v>
       </c>
       <c r="E43" s="50"/>
-      <c r="F43" s="68" t="s">
+      <c r="F43" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="G43" s="68"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
-      <c r="J43" s="68"/>
-      <c r="K43" s="68"/>
-      <c r="L43" s="68"/>
-      <c r="M43" s="68"/>
+      <c r="G43" s="74"/>
+      <c r="H43" s="74"/>
+      <c r="I43" s="74"/>
+      <c r="J43" s="74"/>
+      <c r="K43" s="74"/>
+      <c r="L43" s="74"/>
+      <c r="M43" s="74"/>
     </row>
     <row r="44" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="B44" s="48" t="s">
+      <c r="B44" s="49" t="s">
         <v>100</v>
       </c>
       <c r="C44" s="50"/>
-      <c r="D44" s="48" t="s">
+      <c r="D44" s="49" t="s">
         <v>101</v>
       </c>
       <c r="E44" s="50"/>
-      <c r="F44" s="68" t="s">
+      <c r="F44" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="G44" s="68"/>
-      <c r="H44" s="68"/>
-      <c r="I44" s="68"/>
-      <c r="J44" s="68"/>
-      <c r="K44" s="68"/>
-      <c r="L44" s="68"/>
-      <c r="M44" s="68"/>
+      <c r="G44" s="74"/>
+      <c r="H44" s="74"/>
+      <c r="I44" s="74"/>
+      <c r="J44" s="74"/>
+      <c r="K44" s="74"/>
+      <c r="L44" s="74"/>
+      <c r="M44" s="74"/>
     </row>
     <row r="45" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="60" t="s">
+      <c r="A45" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="60" t="s">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="60"/>
-      <c r="F45" s="60" t="s">
+      <c r="E45" s="54"/>
+      <c r="F45" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="G45" s="60"/>
-      <c r="H45" s="75" t="s">
+      <c r="G45" s="54"/>
+      <c r="H45" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="I45" s="75"/>
-      <c r="J45" s="75" t="s">
+      <c r="I45" s="73"/>
+      <c r="J45" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="K45" s="75"/>
-      <c r="L45" s="75" t="s">
+      <c r="K45" s="73"/>
+      <c r="L45" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="M45" s="75"/>
+      <c r="M45" s="73"/>
     </row>
     <row r="46" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="68" t="s">
+      <c r="A46" s="74" t="s">
         <v>195</v>
       </c>
-      <c r="B46" s="68"/>
-      <c r="C46" s="68"/>
-      <c r="D46" s="68" t="s">
+      <c r="B46" s="74"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68" t="s">
+      <c r="E46" s="74"/>
+      <c r="F46" s="74" t="s">
         <v>104</v>
       </c>
-      <c r="G46" s="68"/>
-      <c r="H46" s="68" t="s">
+      <c r="G46" s="74"/>
+      <c r="H46" s="74" t="s">
         <v>105</v>
       </c>
-      <c r="I46" s="68"/>
-      <c r="J46" s="68" t="s">
+      <c r="I46" s="74"/>
+      <c r="J46" s="74" t="s">
         <v>106</v>
       </c>
-      <c r="K46" s="68"/>
-      <c r="L46" s="68" t="s">
+      <c r="K46" s="74"/>
+      <c r="L46" s="74" t="s">
         <v>107</v>
       </c>
-      <c r="M46" s="68"/>
+      <c r="M46" s="74"/>
     </row>
     <row r="47" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B47" s="56" t="s">
+      <c r="B47" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="57"/>
-      <c r="D47" s="56" t="s">
+      <c r="C47" s="56"/>
+      <c r="D47" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="63"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="58" t="s">
+      <c r="E47" s="67"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="62"/>
-      <c r="I47" s="59"/>
-      <c r="J47" s="58" t="s">
+      <c r="H47" s="66"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="59"/>
-      <c r="L47" s="56" t="s">
+      <c r="K47" s="52"/>
+      <c r="L47" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="M47" s="57"/>
+      <c r="M47" s="56"/>
     </row>
     <row r="48" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="B48" s="48" t="s">
+      <c r="B48" s="49" t="s">
         <v>108</v>
       </c>
       <c r="C48" s="50"/>
-      <c r="D48" s="68" t="s">
+      <c r="D48" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="E48" s="68"/>
-      <c r="F48" s="68"/>
-      <c r="G48" s="68" t="s">
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="74" t="s">
         <v>110</v>
       </c>
-      <c r="H48" s="68"/>
-      <c r="I48" s="68"/>
-      <c r="J48" s="68" t="s">
+      <c r="H48" s="74"/>
+      <c r="I48" s="74"/>
+      <c r="J48" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="K48" s="68"/>
-      <c r="L48" s="68" t="s">
+      <c r="K48" s="74"/>
+      <c r="L48" s="74" t="s">
         <v>112</v>
       </c>
-      <c r="M48" s="68"/>
+      <c r="M48" s="74"/>
     </row>
     <row r="49" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="B49" s="48" t="s">
+      <c r="B49" s="49" t="s">
         <v>113</v>
       </c>
       <c r="C49" s="50"/>
-      <c r="D49" s="68" t="s">
+      <c r="D49" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="E49" s="68"/>
-      <c r="F49" s="68"/>
-      <c r="G49" s="68" t="s">
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="H49" s="68"/>
-      <c r="I49" s="68"/>
-      <c r="J49" s="68"/>
-      <c r="K49" s="68"/>
-      <c r="L49" s="68"/>
-      <c r="M49" s="68"/>
+      <c r="H49" s="74"/>
+      <c r="I49" s="74"/>
+      <c r="J49" s="74"/>
+      <c r="K49" s="74"/>
+      <c r="L49" s="74"/>
+      <c r="M49" s="74"/>
     </row>
     <row r="50" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="B50" s="48" t="s">
+      <c r="B50" s="49" t="s">
         <v>116</v>
       </c>
       <c r="C50" s="50"/>
-      <c r="D50" s="68" t="s">
+      <c r="D50" s="74" t="s">
         <v>117</v>
       </c>
-      <c r="E50" s="68"/>
-      <c r="F50" s="68"/>
-      <c r="G50" s="68" t="s">
+      <c r="E50" s="74"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="H50" s="68"/>
-      <c r="I50" s="68"/>
-      <c r="J50" s="68"/>
-      <c r="K50" s="68"/>
-      <c r="L50" s="68"/>
-      <c r="M50" s="68"/>
+      <c r="H50" s="74"/>
+      <c r="I50" s="74"/>
+      <c r="J50" s="74"/>
+      <c r="K50" s="74"/>
+      <c r="L50" s="74"/>
+      <c r="M50" s="74"/>
     </row>
     <row r="51" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="60" t="s">
+      <c r="A51" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="60"/>
+      <c r="B51" s="54"/>
       <c r="C51" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D51" s="60" t="s">
+      <c r="D51" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="60"/>
-      <c r="F51" s="75" t="s">
+      <c r="E51" s="54"/>
+      <c r="F51" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="G51" s="75"/>
-      <c r="H51" s="75" t="s">
+      <c r="G51" s="73"/>
+      <c r="H51" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="I51" s="75"/>
-      <c r="J51" s="75" t="s">
+      <c r="I51" s="73"/>
+      <c r="J51" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="K51" s="75"/>
-      <c r="L51" s="75" t="s">
+      <c r="K51" s="73"/>
+      <c r="L51" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="M51" s="75"/>
+      <c r="M51" s="73"/>
     </row>
     <row r="52" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="68" t="s">
+      <c r="A52" s="74" t="s">
         <v>196</v>
       </c>
-      <c r="B52" s="68"/>
+      <c r="B52" s="74"/>
       <c r="C52" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D52" s="68" t="s">
+      <c r="D52" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68" t="s">
+      <c r="E52" s="74"/>
+      <c r="F52" s="74" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="68"/>
-      <c r="H52" s="68" t="s">
+      <c r="G52" s="74"/>
+      <c r="H52" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="I52" s="68"/>
-      <c r="J52" s="68" t="s">
+      <c r="I52" s="74"/>
+      <c r="J52" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="K52" s="68"/>
-      <c r="L52" s="68" t="s">
+      <c r="K52" s="74"/>
+      <c r="L52" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="M52" s="68"/>
+      <c r="M52" s="74"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="F53" s="1"/>
@@ -4659,107 +4659,107 @@
       <c r="L54" s="1"/>
     </row>
     <row r="56" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="77" t="s">
+      <c r="A56" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="B56" s="77"/>
-      <c r="C56" s="77"/>
-      <c r="D56" s="77"/>
-      <c r="E56" s="77"/>
-      <c r="F56" s="77"/>
-      <c r="G56" s="77"/>
-      <c r="H56" s="77"/>
-      <c r="I56" s="77"/>
-      <c r="J56" s="77"/>
-      <c r="K56" s="77"/>
-      <c r="L56" s="77"/>
-      <c r="M56" s="77"/>
+      <c r="B56" s="48"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
+      <c r="H56" s="48"/>
+      <c r="I56" s="48"/>
+      <c r="J56" s="48"/>
+      <c r="K56" s="48"/>
+      <c r="L56" s="48"/>
+      <c r="M56" s="48"/>
     </row>
     <row r="57" spans="1:14" ht="386.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="77"/>
-      <c r="B57" s="77"/>
-      <c r="C57" s="77"/>
-      <c r="D57" s="77"/>
-      <c r="E57" s="77"/>
-      <c r="F57" s="77"/>
-      <c r="G57" s="77"/>
-      <c r="H57" s="77"/>
-      <c r="I57" s="77"/>
-      <c r="J57" s="77"/>
-      <c r="K57" s="77"/>
-      <c r="L57" s="77"/>
-      <c r="M57" s="77"/>
+      <c r="A57" s="48"/>
+      <c r="B57" s="48"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="48"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="48"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="48"/>
+      <c r="L57" s="48"/>
+      <c r="M57" s="48"/>
     </row>
     <row r="60" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="55" t="s">
+      <c r="A60" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B60" s="55"/>
-      <c r="C60" s="55"/>
-      <c r="D60" s="55"/>
-      <c r="E60" s="55"/>
-      <c r="F60" s="55"/>
-      <c r="G60" s="55"/>
-      <c r="H60" s="55"/>
-      <c r="I60" s="55"/>
-      <c r="J60" s="55"/>
-      <c r="K60" s="55"/>
-      <c r="L60" s="55"/>
-      <c r="M60" s="55"/>
-      <c r="N60" s="55"/>
+      <c r="B60" s="75"/>
+      <c r="C60" s="75"/>
+      <c r="D60" s="75"/>
+      <c r="E60" s="75"/>
+      <c r="F60" s="75"/>
+      <c r="G60" s="75"/>
+      <c r="H60" s="75"/>
+      <c r="I60" s="75"/>
+      <c r="J60" s="75"/>
+      <c r="K60" s="75"/>
+      <c r="L60" s="75"/>
+      <c r="M60" s="75"/>
+      <c r="N60" s="75"/>
     </row>
     <row r="61" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="64" t="s">
+      <c r="A61" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B61" s="64"/>
-      <c r="C61" s="61" t="s">
+      <c r="B61" s="71"/>
+      <c r="C61" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="D61" s="61"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="61"/>
+      <c r="D61" s="72"/>
+      <c r="E61" s="72"/>
+      <c r="F61" s="72"/>
       <c r="G61" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H61" s="2"/>
-      <c r="I61" s="61" t="s">
+      <c r="I61" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="J61" s="61"/>
-      <c r="K61" s="61"/>
-      <c r="L61" s="61"/>
-      <c r="M61" s="61"/>
+      <c r="J61" s="72"/>
+      <c r="K61" s="72"/>
+      <c r="L61" s="72"/>
+      <c r="M61" s="72"/>
     </row>
     <row r="62" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="64" t="s">
+      <c r="A62" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B62" s="64"/>
-      <c r="C62" s="61" t="s">
+      <c r="B62" s="71"/>
+      <c r="C62" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="D62" s="61"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="61"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="72"/>
+      <c r="F62" s="72"/>
       <c r="G62" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H62" s="2"/>
-      <c r="I62" s="51" t="s">
+      <c r="I62" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="J62" s="51"/>
-      <c r="K62" s="51"/>
-      <c r="L62" s="51"/>
-      <c r="M62" s="51"/>
+      <c r="J62" s="68"/>
+      <c r="K62" s="68"/>
+      <c r="L62" s="68"/>
+      <c r="M62" s="68"/>
     </row>
     <row r="63" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="60" t="s">
+      <c r="A63" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B63" s="60"/>
-      <c r="C63" s="60"/>
+      <c r="B63" s="54"/>
+      <c r="C63" s="54"/>
       <c r="D63" s="76" t="s">
         <v>43</v>
       </c>
@@ -4767,592 +4767,592 @@
       <c r="F63" s="76"/>
       <c r="G63" s="76"/>
       <c r="H63" s="76"/>
-      <c r="I63" s="60" t="s">
+      <c r="I63" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="J63" s="60"/>
-      <c r="K63" s="68" t="s">
+      <c r="J63" s="54"/>
+      <c r="K63" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="L63" s="68"/>
-      <c r="M63" s="68"/>
+      <c r="L63" s="74"/>
+      <c r="M63" s="74"/>
     </row>
     <row r="64" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="60" t="s">
+      <c r="A64" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B64" s="60"/>
-      <c r="C64" s="60"/>
-      <c r="D64" s="68" t="s">
+      <c r="B64" s="54"/>
+      <c r="C64" s="54"/>
+      <c r="D64" s="74" t="s">
         <v>179</v>
       </c>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
-      <c r="H64" s="68"/>
-      <c r="I64" s="60" t="s">
+      <c r="E64" s="74"/>
+      <c r="F64" s="74"/>
+      <c r="G64" s="74"/>
+      <c r="H64" s="74"/>
+      <c r="I64" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="J64" s="60"/>
-      <c r="K64" s="68">
+      <c r="J64" s="54"/>
+      <c r="K64" s="74">
         <v>1</v>
       </c>
-      <c r="L64" s="68"/>
-      <c r="M64" s="68"/>
+      <c r="L64" s="74"/>
+      <c r="M64" s="74"/>
     </row>
     <row r="65" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="60" t="s">
+      <c r="A65" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="B65" s="60"/>
-      <c r="C65" s="60"/>
-      <c r="D65" s="75" t="s">
+      <c r="B65" s="54"/>
+      <c r="C65" s="54"/>
+      <c r="D65" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="E65" s="75"/>
-      <c r="F65" s="75"/>
-      <c r="G65" s="75"/>
-      <c r="H65" s="75"/>
-      <c r="I65" s="75" t="s">
+      <c r="E65" s="73"/>
+      <c r="F65" s="73"/>
+      <c r="G65" s="73"/>
+      <c r="H65" s="73"/>
+      <c r="I65" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="J65" s="75"/>
-      <c r="K65" s="75"/>
-      <c r="L65" s="75"/>
-      <c r="M65" s="75"/>
+      <c r="J65" s="73"/>
+      <c r="K65" s="73"/>
+      <c r="L65" s="73"/>
+      <c r="M65" s="73"/>
     </row>
     <row r="66" spans="1:13" ht="18" x14ac:dyDescent="0.2">
-      <c r="A66" s="68" t="s">
+      <c r="A66" s="74" t="s">
         <v>192</v>
       </c>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68"/>
-      <c r="D66" s="68" t="s">
+      <c r="B66" s="74"/>
+      <c r="C66" s="74"/>
+      <c r="D66" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="68"/>
-      <c r="H66" s="68"/>
-      <c r="I66" s="68" t="s">
+      <c r="E66" s="74"/>
+      <c r="F66" s="74"/>
+      <c r="G66" s="74"/>
+      <c r="H66" s="74"/>
+      <c r="I66" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="J66" s="68"/>
-      <c r="K66" s="68"/>
-      <c r="L66" s="68"/>
-      <c r="M66" s="68"/>
+      <c r="J66" s="74"/>
+      <c r="K66" s="74"/>
+      <c r="L66" s="74"/>
+      <c r="M66" s="74"/>
     </row>
     <row r="67" spans="1:13" ht="18" x14ac:dyDescent="0.2">
-      <c r="A67" s="68" t="s">
+      <c r="A67" s="74" t="s">
         <v>193</v>
       </c>
-      <c r="B67" s="68"/>
-      <c r="C67" s="68"/>
-      <c r="D67" s="68" t="s">
+      <c r="B67" s="74"/>
+      <c r="C67" s="74"/>
+      <c r="D67" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
-      <c r="H67" s="68"/>
-      <c r="I67" s="68" t="s">
+      <c r="E67" s="74"/>
+      <c r="F67" s="74"/>
+      <c r="G67" s="74"/>
+      <c r="H67" s="74"/>
+      <c r="I67" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="J67" s="68"/>
-      <c r="K67" s="68"/>
-      <c r="L67" s="68"/>
-      <c r="M67" s="68"/>
+      <c r="J67" s="74"/>
+      <c r="K67" s="74"/>
+      <c r="L67" s="74"/>
+      <c r="M67" s="74"/>
     </row>
     <row r="68" spans="1:13" ht="18" x14ac:dyDescent="0.2">
-      <c r="A68" s="68" t="s">
+      <c r="A68" s="74" t="s">
         <v>191</v>
       </c>
-      <c r="B68" s="68"/>
-      <c r="C68" s="68"/>
-      <c r="D68" s="68" t="s">
+      <c r="B68" s="74"/>
+      <c r="C68" s="74"/>
+      <c r="D68" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
-      <c r="H68" s="68"/>
-      <c r="I68" s="68" t="s">
+      <c r="E68" s="74"/>
+      <c r="F68" s="74"/>
+      <c r="G68" s="74"/>
+      <c r="H68" s="74"/>
+      <c r="I68" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="J68" s="68"/>
-      <c r="K68" s="68"/>
-      <c r="L68" s="68"/>
-      <c r="M68" s="68"/>
+      <c r="J68" s="74"/>
+      <c r="K68" s="74"/>
+      <c r="L68" s="74"/>
+      <c r="M68" s="74"/>
     </row>
     <row r="69" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B69" s="75" t="s">
+      <c r="B69" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="C69" s="75"/>
-      <c r="D69" s="75" t="s">
+      <c r="C69" s="73"/>
+      <c r="D69" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="E69" s="75"/>
-      <c r="F69" s="75"/>
-      <c r="G69" s="60" t="s">
+      <c r="E69" s="73"/>
+      <c r="F69" s="73"/>
+      <c r="G69" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="H69" s="60"/>
-      <c r="I69" s="60" t="s">
+      <c r="H69" s="54"/>
+      <c r="I69" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="60"/>
-      <c r="K69" s="75" t="s">
+      <c r="J69" s="54"/>
+      <c r="K69" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="L69" s="75"/>
-      <c r="M69" s="75"/>
+      <c r="L69" s="73"/>
+      <c r="M69" s="73"/>
     </row>
     <row r="70" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="B70" s="68" t="s">
+      <c r="B70" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="C70" s="68"/>
-      <c r="D70" s="68" t="s">
+      <c r="C70" s="74"/>
+      <c r="D70" s="74" t="s">
         <v>131</v>
       </c>
-      <c r="E70" s="68"/>
-      <c r="F70" s="68"/>
-      <c r="G70" s="68" t="s">
+      <c r="E70" s="74"/>
+      <c r="F70" s="74"/>
+      <c r="G70" s="74" t="s">
         <v>132</v>
       </c>
-      <c r="H70" s="68"/>
-      <c r="I70" s="68" t="s">
+      <c r="H70" s="74"/>
+      <c r="I70" s="74" t="s">
         <v>133</v>
       </c>
-      <c r="J70" s="68"/>
-      <c r="K70" s="68" t="s">
+      <c r="J70" s="74"/>
+      <c r="K70" s="74" t="s">
         <v>134</v>
       </c>
-      <c r="L70" s="68"/>
-      <c r="M70" s="68"/>
+      <c r="L70" s="74"/>
+      <c r="M70" s="74"/>
     </row>
     <row r="71" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="B71" s="68" t="s">
+      <c r="B71" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="C71" s="68"/>
-      <c r="D71" s="68" t="s">
+      <c r="C71" s="74"/>
+      <c r="D71" s="74" t="s">
         <v>136</v>
       </c>
-      <c r="E71" s="68"/>
-      <c r="F71" s="68"/>
-      <c r="G71" s="68" t="s">
+      <c r="E71" s="74"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="H71" s="68"/>
-      <c r="I71" s="68"/>
-      <c r="J71" s="68"/>
-      <c r="K71" s="68"/>
-      <c r="L71" s="68"/>
-      <c r="M71" s="68"/>
+      <c r="H71" s="74"/>
+      <c r="I71" s="74"/>
+      <c r="J71" s="74"/>
+      <c r="K71" s="74"/>
+      <c r="L71" s="74"/>
+      <c r="M71" s="74"/>
     </row>
     <row r="72" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="B72" s="68" t="s">
+      <c r="B72" s="74" t="s">
         <v>138</v>
       </c>
-      <c r="C72" s="68"/>
-      <c r="D72" s="68" t="s">
+      <c r="C72" s="74"/>
+      <c r="D72" s="74" t="s">
         <v>139</v>
       </c>
-      <c r="E72" s="68"/>
-      <c r="F72" s="68"/>
-      <c r="G72" s="68" t="s">
+      <c r="E72" s="74"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="74" t="s">
         <v>140</v>
       </c>
-      <c r="H72" s="68"/>
-      <c r="I72" s="68"/>
-      <c r="J72" s="68"/>
-      <c r="K72" s="68"/>
-      <c r="L72" s="68"/>
-      <c r="M72" s="68"/>
+      <c r="H72" s="74"/>
+      <c r="I72" s="74"/>
+      <c r="J72" s="74"/>
+      <c r="K72" s="74"/>
+      <c r="L72" s="74"/>
+      <c r="M72" s="74"/>
     </row>
     <row r="73" spans="1:13" ht="36" x14ac:dyDescent="0.2">
-      <c r="A73" s="60" t="s">
+      <c r="A73" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="B73" s="60"/>
+      <c r="B73" s="54"/>
       <c r="C73" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D73" s="60" t="s">
+      <c r="D73" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="E73" s="60"/>
-      <c r="F73" s="75" t="s">
+      <c r="E73" s="54"/>
+      <c r="F73" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="G73" s="75"/>
-      <c r="H73" s="75" t="s">
+      <c r="G73" s="73"/>
+      <c r="H73" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="I73" s="75"/>
-      <c r="J73" s="75" t="s">
+      <c r="I73" s="73"/>
+      <c r="J73" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="K73" s="75"/>
-      <c r="L73" s="75" t="s">
+      <c r="K73" s="73"/>
+      <c r="L73" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="M73" s="75"/>
+      <c r="M73" s="73"/>
     </row>
     <row r="74" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="68" t="s">
+      <c r="A74" s="74" t="s">
         <v>197</v>
       </c>
-      <c r="B74" s="68"/>
+      <c r="B74" s="74"/>
       <c r="C74" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="68" t="s">
+      <c r="D74" s="74" t="s">
         <v>141</v>
       </c>
-      <c r="E74" s="68"/>
-      <c r="F74" s="68" t="s">
+      <c r="E74" s="74"/>
+      <c r="F74" s="74" t="s">
         <v>142</v>
       </c>
-      <c r="G74" s="68"/>
-      <c r="H74" s="68" t="s">
+      <c r="G74" s="74"/>
+      <c r="H74" s="74" t="s">
         <v>143</v>
       </c>
-      <c r="I74" s="68"/>
-      <c r="J74" s="68" t="s">
+      <c r="I74" s="74"/>
+      <c r="J74" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="K74" s="68"/>
-      <c r="L74" s="68" t="s">
+      <c r="K74" s="74"/>
+      <c r="L74" s="74" t="s">
         <v>145</v>
       </c>
-      <c r="M74" s="68"/>
+      <c r="M74" s="74"/>
     </row>
     <row r="75" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B75" s="75" t="s">
+      <c r="B75" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C75" s="75"/>
-      <c r="D75" s="75" t="s">
+      <c r="C75" s="73"/>
+      <c r="D75" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="E75" s="75"/>
-      <c r="F75" s="60" t="s">
+      <c r="E75" s="73"/>
+      <c r="F75" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G75" s="60"/>
-      <c r="H75" s="60" t="s">
+      <c r="G75" s="54"/>
+      <c r="H75" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="I75" s="60"/>
-      <c r="J75" s="60"/>
-      <c r="K75" s="75" t="s">
+      <c r="I75" s="54"/>
+      <c r="J75" s="54"/>
+      <c r="K75" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="L75" s="75"/>
-      <c r="M75" s="75"/>
+      <c r="L75" s="73"/>
+      <c r="M75" s="73"/>
     </row>
     <row r="76" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="B76" s="68" t="s">
+      <c r="B76" s="74" t="s">
         <v>146</v>
       </c>
-      <c r="C76" s="68"/>
-      <c r="D76" s="68" t="s">
+      <c r="C76" s="74"/>
+      <c r="D76" s="74" t="s">
         <v>147</v>
       </c>
-      <c r="E76" s="68"/>
-      <c r="F76" s="68" t="s">
+      <c r="E76" s="74"/>
+      <c r="F76" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="G76" s="68"/>
-      <c r="H76" s="68" t="s">
+      <c r="G76" s="74"/>
+      <c r="H76" s="74" t="s">
         <v>149</v>
       </c>
-      <c r="I76" s="68"/>
-      <c r="J76" s="68"/>
-      <c r="K76" s="68" t="s">
+      <c r="I76" s="74"/>
+      <c r="J76" s="74"/>
+      <c r="K76" s="74" t="s">
         <v>150</v>
       </c>
-      <c r="L76" s="68"/>
-      <c r="M76" s="68"/>
+      <c r="L76" s="74"/>
+      <c r="M76" s="74"/>
     </row>
     <row r="77" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="B77" s="68" t="s">
+      <c r="B77" s="74" t="s">
         <v>151</v>
       </c>
-      <c r="C77" s="68"/>
-      <c r="D77" s="68" t="s">
+      <c r="C77" s="74"/>
+      <c r="D77" s="74" t="s">
         <v>152</v>
       </c>
-      <c r="E77" s="68"/>
-      <c r="F77" s="68" t="s">
+      <c r="E77" s="74"/>
+      <c r="F77" s="74" t="s">
         <v>153</v>
       </c>
-      <c r="G77" s="68"/>
-      <c r="H77" s="68"/>
-      <c r="I77" s="68"/>
-      <c r="J77" s="68"/>
-      <c r="K77" s="68"/>
-      <c r="L77" s="68"/>
-      <c r="M77" s="68"/>
+      <c r="G77" s="74"/>
+      <c r="H77" s="74"/>
+      <c r="I77" s="74"/>
+      <c r="J77" s="74"/>
+      <c r="K77" s="74"/>
+      <c r="L77" s="74"/>
+      <c r="M77" s="74"/>
     </row>
     <row r="78" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="B78" s="68" t="s">
+      <c r="B78" s="74" t="s">
         <v>154</v>
       </c>
-      <c r="C78" s="68"/>
-      <c r="D78" s="68" t="s">
+      <c r="C78" s="74"/>
+      <c r="D78" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="E78" s="68"/>
-      <c r="F78" s="68" t="s">
+      <c r="E78" s="74"/>
+      <c r="F78" s="74" t="s">
         <v>156</v>
       </c>
-      <c r="G78" s="68"/>
-      <c r="H78" s="68"/>
-      <c r="I78" s="68"/>
-      <c r="J78" s="68"/>
-      <c r="K78" s="68"/>
-      <c r="L78" s="68"/>
-      <c r="M78" s="68"/>
+      <c r="G78" s="74"/>
+      <c r="H78" s="74"/>
+      <c r="I78" s="74"/>
+      <c r="J78" s="74"/>
+      <c r="K78" s="74"/>
+      <c r="L78" s="74"/>
+      <c r="M78" s="74"/>
     </row>
     <row r="79" spans="1:13" ht="18" x14ac:dyDescent="0.2">
-      <c r="A79" s="60" t="s">
+      <c r="A79" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="B79" s="60"/>
-      <c r="C79" s="60"/>
-      <c r="D79" s="60" t="s">
+      <c r="B79" s="54"/>
+      <c r="C79" s="54"/>
+      <c r="D79" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="E79" s="60"/>
-      <c r="F79" s="60" t="s">
+      <c r="E79" s="54"/>
+      <c r="F79" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="G79" s="60"/>
-      <c r="H79" s="75" t="s">
+      <c r="G79" s="54"/>
+      <c r="H79" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="I79" s="75"/>
-      <c r="J79" s="75" t="s">
+      <c r="I79" s="73"/>
+      <c r="J79" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="K79" s="75"/>
-      <c r="L79" s="75" t="s">
+      <c r="K79" s="73"/>
+      <c r="L79" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="M79" s="75"/>
+      <c r="M79" s="73"/>
     </row>
     <row r="80" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="68" t="s">
+      <c r="A80" s="74" t="s">
         <v>198</v>
       </c>
-      <c r="B80" s="68"/>
-      <c r="C80" s="68"/>
-      <c r="D80" s="68" t="s">
+      <c r="B80" s="74"/>
+      <c r="C80" s="74"/>
+      <c r="D80" s="74" t="s">
         <v>157</v>
       </c>
-      <c r="E80" s="68"/>
-      <c r="F80" s="68" t="s">
+      <c r="E80" s="74"/>
+      <c r="F80" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="G80" s="68"/>
-      <c r="H80" s="68" t="s">
+      <c r="G80" s="74"/>
+      <c r="H80" s="74" t="s">
         <v>159</v>
       </c>
-      <c r="I80" s="68"/>
-      <c r="J80" s="68" t="s">
+      <c r="I80" s="74"/>
+      <c r="J80" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="K80" s="68"/>
-      <c r="L80" s="68" t="s">
+      <c r="K80" s="74"/>
+      <c r="L80" s="74" t="s">
         <v>161</v>
       </c>
-      <c r="M80" s="68"/>
+      <c r="M80" s="74"/>
     </row>
     <row r="81" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B81" s="75" t="s">
+      <c r="B81" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="C81" s="75"/>
-      <c r="D81" s="75" t="s">
+      <c r="C81" s="73"/>
+      <c r="D81" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="E81" s="75"/>
-      <c r="F81" s="60" t="s">
+      <c r="E81" s="73"/>
+      <c r="F81" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G81" s="60"/>
-      <c r="H81" s="60" t="s">
+      <c r="G81" s="54"/>
+      <c r="H81" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="I81" s="60"/>
-      <c r="J81" s="60"/>
-      <c r="K81" s="75" t="s">
+      <c r="I81" s="54"/>
+      <c r="J81" s="54"/>
+      <c r="K81" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="L81" s="75"/>
-      <c r="M81" s="75"/>
+      <c r="L81" s="73"/>
+      <c r="M81" s="73"/>
     </row>
     <row r="82" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="B82" s="68" t="s">
+      <c r="B82" s="74" t="s">
         <v>162</v>
       </c>
-      <c r="C82" s="68"/>
-      <c r="D82" s="68" t="s">
+      <c r="C82" s="74"/>
+      <c r="D82" s="74" t="s">
         <v>163</v>
       </c>
-      <c r="E82" s="68"/>
-      <c r="F82" s="68" t="s">
+      <c r="E82" s="74"/>
+      <c r="F82" s="74" t="s">
         <v>164</v>
       </c>
-      <c r="G82" s="68"/>
-      <c r="H82" s="68" t="s">
+      <c r="G82" s="74"/>
+      <c r="H82" s="74" t="s">
         <v>165</v>
       </c>
-      <c r="I82" s="68"/>
-      <c r="J82" s="68"/>
-      <c r="K82" s="68" t="s">
+      <c r="I82" s="74"/>
+      <c r="J82" s="74"/>
+      <c r="K82" s="74" t="s">
         <v>166</v>
       </c>
-      <c r="L82" s="68"/>
-      <c r="M82" s="68"/>
+      <c r="L82" s="74"/>
+      <c r="M82" s="74"/>
     </row>
     <row r="83" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="B83" s="68" t="s">
+      <c r="B83" s="74" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="68"/>
-      <c r="D83" s="68" t="s">
+      <c r="C83" s="74"/>
+      <c r="D83" s="74" t="s">
         <v>168</v>
       </c>
-      <c r="E83" s="68"/>
-      <c r="F83" s="68" t="s">
+      <c r="E83" s="74"/>
+      <c r="F83" s="74" t="s">
         <v>169</v>
       </c>
-      <c r="G83" s="68"/>
-      <c r="H83" s="68"/>
-      <c r="I83" s="68"/>
-      <c r="J83" s="68"/>
-      <c r="K83" s="68"/>
-      <c r="L83" s="68"/>
-      <c r="M83" s="68"/>
+      <c r="G83" s="74"/>
+      <c r="H83" s="74"/>
+      <c r="I83" s="74"/>
+      <c r="J83" s="74"/>
+      <c r="K83" s="74"/>
+      <c r="L83" s="74"/>
+      <c r="M83" s="74"/>
     </row>
     <row r="84" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="B84" s="68" t="s">
+      <c r="B84" s="74" t="s">
         <v>170</v>
       </c>
-      <c r="C84" s="68"/>
-      <c r="D84" s="68" t="s">
+      <c r="C84" s="74"/>
+      <c r="D84" s="74" t="s">
         <v>171</v>
       </c>
-      <c r="E84" s="68"/>
-      <c r="F84" s="68" t="s">
+      <c r="E84" s="74"/>
+      <c r="F84" s="74" t="s">
         <v>172</v>
       </c>
-      <c r="G84" s="68"/>
-      <c r="H84" s="68"/>
-      <c r="I84" s="68"/>
-      <c r="J84" s="68"/>
-      <c r="K84" s="68"/>
-      <c r="L84" s="68"/>
-      <c r="M84" s="68"/>
+      <c r="G84" s="74"/>
+      <c r="H84" s="74"/>
+      <c r="I84" s="74"/>
+      <c r="J84" s="74"/>
+      <c r="K84" s="74"/>
+      <c r="L84" s="74"/>
+      <c r="M84" s="74"/>
     </row>
     <row r="85" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="60" t="s">
+      <c r="A85" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="B85" s="60"/>
+      <c r="B85" s="54"/>
       <c r="C85" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D85" s="60" t="s">
+      <c r="D85" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="E85" s="60"/>
-      <c r="F85" s="75" t="s">
+      <c r="E85" s="54"/>
+      <c r="F85" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="G85" s="75"/>
-      <c r="H85" s="75" t="s">
+      <c r="G85" s="73"/>
+      <c r="H85" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="I85" s="75"/>
-      <c r="J85" s="75" t="s">
+      <c r="I85" s="73"/>
+      <c r="J85" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="K85" s="75"/>
-      <c r="L85" s="75" t="s">
+      <c r="K85" s="73"/>
+      <c r="L85" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="M85" s="75"/>
+      <c r="M85" s="73"/>
     </row>
     <row r="86" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="68" t="s">
+      <c r="A86" s="74" t="s">
         <v>199</v>
       </c>
-      <c r="B86" s="68"/>
+      <c r="B86" s="74"/>
       <c r="C86" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D86" s="68" t="s">
+      <c r="D86" s="74" t="s">
         <v>173</v>
       </c>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68" t="s">
+      <c r="E86" s="74"/>
+      <c r="F86" s="74" t="s">
         <v>205</v>
       </c>
-      <c r="G86" s="68"/>
-      <c r="H86" s="68" t="s">
+      <c r="G86" s="74"/>
+      <c r="H86" s="74" t="s">
         <v>204</v>
       </c>
-      <c r="I86" s="68"/>
-      <c r="J86" s="68" t="s">
+      <c r="I86" s="74"/>
+      <c r="J86" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="K86" s="68"/>
-      <c r="L86" s="68" t="s">
+      <c r="K86" s="74"/>
+      <c r="L86" s="74" t="s">
         <v>175</v>
       </c>
-      <c r="M86" s="68"/>
+      <c r="M86" s="74"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="F87" s="1"/>
@@ -5376,101 +5376,101 @@
     </row>
     <row r="90" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="91" spans="1:14" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="77" t="s">
+      <c r="A91" s="48" t="s">
         <v>202</v>
       </c>
-      <c r="B91" s="77"/>
-      <c r="C91" s="77"/>
-      <c r="D91" s="77"/>
-      <c r="E91" s="77"/>
-      <c r="F91" s="77"/>
-      <c r="G91" s="77"/>
-      <c r="H91" s="77"/>
-      <c r="I91" s="77"/>
-      <c r="J91" s="77"/>
-      <c r="K91" s="77"/>
-      <c r="L91" s="77"/>
-      <c r="M91" s="77"/>
+      <c r="B91" s="48"/>
+      <c r="C91" s="48"/>
+      <c r="D91" s="48"/>
+      <c r="E91" s="48"/>
+      <c r="F91" s="48"/>
+      <c r="G91" s="48"/>
+      <c r="H91" s="48"/>
+      <c r="I91" s="48"/>
+      <c r="J91" s="48"/>
+      <c r="K91" s="48"/>
+      <c r="L91" s="48"/>
+      <c r="M91" s="48"/>
     </row>
     <row r="92" spans="1:14" ht="378" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="77"/>
-      <c r="B92" s="77"/>
-      <c r="C92" s="77"/>
-      <c r="D92" s="77"/>
-      <c r="E92" s="77"/>
-      <c r="F92" s="77"/>
-      <c r="G92" s="77"/>
-      <c r="H92" s="77"/>
-      <c r="I92" s="77"/>
-      <c r="J92" s="77"/>
-      <c r="K92" s="77"/>
-      <c r="L92" s="77"/>
-      <c r="M92" s="77"/>
+      <c r="A92" s="48"/>
+      <c r="B92" s="48"/>
+      <c r="C92" s="48"/>
+      <c r="D92" s="48"/>
+      <c r="E92" s="48"/>
+      <c r="F92" s="48"/>
+      <c r="G92" s="48"/>
+      <c r="H92" s="48"/>
+      <c r="I92" s="48"/>
+      <c r="J92" s="48"/>
+      <c r="K92" s="48"/>
+      <c r="L92" s="48"/>
+      <c r="M92" s="48"/>
     </row>
     <row r="94" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="55" t="s">
+      <c r="A94" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B94" s="55"/>
-      <c r="C94" s="55"/>
-      <c r="D94" s="55"/>
-      <c r="E94" s="55"/>
-      <c r="F94" s="55"/>
-      <c r="G94" s="55"/>
-      <c r="H94" s="55"/>
-      <c r="I94" s="55"/>
-      <c r="J94" s="55"/>
-      <c r="K94" s="55"/>
-      <c r="L94" s="55"/>
-      <c r="M94" s="55"/>
-      <c r="N94" s="55"/>
+      <c r="B94" s="75"/>
+      <c r="C94" s="75"/>
+      <c r="D94" s="75"/>
+      <c r="E94" s="75"/>
+      <c r="F94" s="75"/>
+      <c r="G94" s="75"/>
+      <c r="H94" s="75"/>
+      <c r="I94" s="75"/>
+      <c r="J94" s="75"/>
+      <c r="K94" s="75"/>
+      <c r="L94" s="75"/>
+      <c r="M94" s="75"/>
+      <c r="N94" s="75"/>
     </row>
     <row r="95" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="81" t="s">
+      <c r="A95" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B95" s="81"/>
-      <c r="C95" s="68" t="s">
+      <c r="B95" s="79"/>
+      <c r="C95" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="68"/>
+      <c r="D95" s="74"/>
+      <c r="E95" s="74"/>
+      <c r="F95" s="74"/>
       <c r="G95" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H95" s="5"/>
-      <c r="I95" s="68" t="s">
+      <c r="I95" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="J95" s="68"/>
-      <c r="K95" s="68"/>
-      <c r="L95" s="68"/>
-      <c r="M95" s="68"/>
+      <c r="J95" s="74"/>
+      <c r="K95" s="74"/>
+      <c r="L95" s="74"/>
+      <c r="M95" s="74"/>
       <c r="N95" s="34"/>
     </row>
     <row r="96" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="81" t="s">
+      <c r="A96" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="B96" s="81"/>
-      <c r="C96" s="68" t="s">
+      <c r="B96" s="79"/>
+      <c r="C96" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="D96" s="68"/>
-      <c r="E96" s="68"/>
-      <c r="F96" s="68"/>
+      <c r="D96" s="74"/>
+      <c r="E96" s="74"/>
+      <c r="F96" s="74"/>
       <c r="G96" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H96" s="5"/>
-      <c r="I96" s="68" t="s">
+      <c r="I96" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="J96" s="68"/>
-      <c r="K96" s="68"/>
-      <c r="L96" s="68"/>
-      <c r="M96" s="68"/>
+      <c r="J96" s="74"/>
+      <c r="K96" s="74"/>
+      <c r="L96" s="74"/>
+      <c r="M96" s="74"/>
       <c r="N96" s="34"/>
     </row>
     <row r="97" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -5546,6 +5546,264 @@
     </row>
   </sheetData>
   <mergeCells count="282">
+    <mergeCell ref="L85:M85"/>
+    <mergeCell ref="L86:M86"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="K76:M78"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="H81:J81"/>
+    <mergeCell ref="H82:J84"/>
+    <mergeCell ref="K81:M81"/>
+    <mergeCell ref="K82:M84"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="L79:M79"/>
+    <mergeCell ref="L80:M80"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="H76:J78"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="K75:M75"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="L48:M50"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="D37:M37"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A31:N31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="I32:M32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="I33:M33"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:F95"/>
+    <mergeCell ref="I95:M95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:F96"/>
+    <mergeCell ref="I96:M96"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="K8:M10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="I17:M17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="I18:M18"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="K23:M25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J25"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="D39:M39"/>
+    <mergeCell ref="D40:M40"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="L42:M44"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I42:K44"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="D38:M38"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A56:M57"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="J48:K50"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A60:N60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="I61:M61"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="I62:M62"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="I66:M66"/>
+    <mergeCell ref="D63:H63"/>
+    <mergeCell ref="D64:H64"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K63:M63"/>
+    <mergeCell ref="K64:M64"/>
+    <mergeCell ref="D65:H65"/>
+    <mergeCell ref="I65:M65"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="D67:H67"/>
+    <mergeCell ref="D68:H68"/>
+    <mergeCell ref="I67:M67"/>
+    <mergeCell ref="I68:M68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="I70:J72"/>
+    <mergeCell ref="K69:M69"/>
+    <mergeCell ref="K70:M72"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="B75:C75"/>
@@ -5570,264 +5828,6 @@
     <mergeCell ref="G72:H72"/>
     <mergeCell ref="L73:M73"/>
     <mergeCell ref="L74:M74"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="D67:H67"/>
-    <mergeCell ref="D68:H68"/>
-    <mergeCell ref="I67:M67"/>
-    <mergeCell ref="I68:M68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="I69:J69"/>
-    <mergeCell ref="I70:J72"/>
-    <mergeCell ref="K69:M69"/>
-    <mergeCell ref="K70:M72"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A60:N60"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="I61:M61"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="I62:M62"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="I66:M66"/>
-    <mergeCell ref="D63:H63"/>
-    <mergeCell ref="D64:H64"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="K63:M63"/>
-    <mergeCell ref="K64:M64"/>
-    <mergeCell ref="D65:H65"/>
-    <mergeCell ref="I65:M65"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A56:M57"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="J48:K50"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="D39:M39"/>
-    <mergeCell ref="D40:M40"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="L42:M44"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I42:K44"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="D38:M38"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="K23:M25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J25"/>
-    <mergeCell ref="K8:M10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="A16:N16"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="I17:M17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="I18:M18"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="C95:F95"/>
-    <mergeCell ref="I95:M95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:F96"/>
-    <mergeCell ref="I96:M96"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A28:M28"/>
-    <mergeCell ref="A31:N31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="I32:M32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="I33:M33"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="D37:M37"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="L48:M50"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="K75:M75"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="H75:J75"/>
-    <mergeCell ref="H76:J78"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="K76:M78"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="H81:J81"/>
-    <mergeCell ref="H82:J84"/>
-    <mergeCell ref="K81:M81"/>
-    <mergeCell ref="K82:M84"/>
-    <mergeCell ref="D79:E79"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="J79:K79"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="L79:M79"/>
-    <mergeCell ref="L80:M80"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="L85:M85"/>
-    <mergeCell ref="L86:M86"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="J86:K86"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5862,76 +5862,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="75" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
     </row>
     <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="68" t="s">
+      <c r="B2" s="79"/>
+      <c r="C2" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
       <c r="G2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="5"/>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
       <c r="N2" s="37"/>
     </row>
     <row r="3" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="68" t="s">
+      <c r="B3" s="79"/>
+      <c r="C3" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
       <c r="G3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="5"/>
-      <c r="I3" s="68" t="s">
+      <c r="I3" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="74"/>
       <c r="N3" s="37"/>
     </row>
     <row r="4" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="73" t="s">
         <v>221</v>
       </c>
-      <c r="B4" s="75"/>
+      <c r="B4" s="73"/>
       <c r="C4" s="38" t="s">
         <v>219</v>
       </c>
@@ -6004,27 +6004,27 @@
       <c r="N5" s="37"/>
     </row>
     <row r="6" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="73" t="s">
         <v>232</v>
       </c>
-      <c r="B6" s="75"/>
-      <c r="C6" s="60" t="s">
+      <c r="B6" s="73"/>
+      <c r="C6" s="54" t="s">
         <v>247</v>
       </c>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60" t="s">
+      <c r="D6" s="54"/>
+      <c r="E6" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60" t="s">
+      <c r="F6" s="54"/>
+      <c r="G6" s="54" t="s">
         <v>230</v>
       </c>
-      <c r="H6" s="60"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
       <c r="N6" s="37"/>
     </row>
     <row r="7" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -6044,29 +6044,29 @@
         <v>233</v>
       </c>
       <c r="H7" s="83"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="68"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
       <c r="N7" s="37"/>
     </row>
     <row r="8" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="51" t="s">
         <v>244</v>
       </c>
-      <c r="B8" s="62"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="62"/>
-      <c r="M8" s="59"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="52"/>
     </row>
     <row r="9" spans="1:14" ht="72" x14ac:dyDescent="0.2">
       <c r="A9" s="42" t="s">
@@ -6126,6 +6126,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="I3:M3"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="C6:D6"/>
@@ -6139,16 +6146,9 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="I6:M7"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.4" right="0.4" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.2" header="0" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>